--- a/src/attributions/attributions_saliency_traj_125.xlsx
+++ b/src/attributions/attributions_saliency_traj_125.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.528184657217935e-05</v>
+        <v>4.01965052442889e-23</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0003092768602073193</v>
+        <v>6.838829562687998e-23</v>
       </c>
       <c r="C4" t="n">
-        <v>8.589486969867721e-05</v>
+        <v>2.993388871757581e-23</v>
       </c>
       <c r="D4" t="n">
-        <v>2.205976670666132e-05</v>
+        <v>7.58725787552845e-23</v>
       </c>
       <c r="E4" t="n">
-        <v>1.679098204476759e-06</v>
+        <v>2.547888195231791e-24</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003545141953509301</v>
+        <v>1.970767338847324e-23</v>
       </c>
       <c r="G4" t="n">
-        <v>3.664246833068319e-05</v>
+        <v>6.684072723567912e-23</v>
       </c>
       <c r="H4" t="n">
-        <v>8.384248940274119e-05</v>
+        <v>6.789947323379435e-23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001115406048484147</v>
+        <v>8.274156931027835e-25</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001044676391757093</v>
+        <v>2.655604943029186e-23</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001272399822482839</v>
+        <v>1.124440062382623e-22</v>
       </c>
       <c r="L4" t="n">
-        <v>9.706058335723355e-05</v>
+        <v>2.663326313569489e-23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001147365474025719</v>
+        <v>7.937007877555962e-23</v>
       </c>
       <c r="N4" t="n">
-        <v>3.707739779201802e-06</v>
+        <v>4.548404740992447e-24</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001929680729517713</v>
+        <v>7.961196088404029e-24</v>
       </c>
       <c r="P4" t="n">
-        <v>4.64693657704629e-05</v>
+        <v>9.213006168969053e-23</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.403710671700537e-05</v>
+        <v>8.509377582480464e-23</v>
       </c>
       <c r="R4" t="n">
-        <v>2.290012525918428e-05</v>
+        <v>3.670964853534703e-23</v>
       </c>
       <c r="S4" t="n">
-        <v>5.753504410677124e-06</v>
+        <v>1.454233129908274e-24</v>
       </c>
       <c r="T4" t="n">
-        <v>3.526228829286993e-05</v>
+        <v>5.722186853928069e-23</v>
       </c>
       <c r="U4" t="n">
-        <v>6.223584205145016e-05</v>
+        <v>2.867286616158743e-23</v>
       </c>
       <c r="V4" t="n">
-        <v>5.530462658498436e-05</v>
+        <v>4.287766044540511e-23</v>
       </c>
       <c r="W4" t="n">
-        <v>8.364637324120849e-05</v>
+        <v>7.149542309504105e-23</v>
       </c>
       <c r="X4" t="n">
-        <v>3.830437708529644e-05</v>
+        <v>2.289990474881136e-23</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.840850695269182e-05</v>
+        <v>2.261718173354558e-23</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.411616803030483e-05</v>
+        <v>2.313674919155129e-23</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.987337964237668e-05</v>
+        <v>9.571153122016099e-24</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.067949288990349e-05</v>
+        <v>3.835043346427423e-24</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.302450800721999e-05</v>
+        <v>6.126727347899887e-23</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0001200905244331807</v>
+        <v>6.079187355421558e-24</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.571547808358446e-05</v>
+        <v>9.912520056976009e-24</v>
       </c>
       <c r="AF4" t="n">
-        <v>6.42307277303189e-05</v>
+        <v>2.09334748827653e-23</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.433331064821687e-05</v>
+        <v>2.579793990087817e-23</v>
       </c>
       <c r="AH4" t="n">
-        <v>9.592899004928768e-05</v>
+        <v>4.147704421907245e-23</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.514966374495998e-05</v>
+        <v>9.764254438700625e-24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.889401210064534e-05</v>
+        <v>2.179852239649075e-24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.637789864616934e-05</v>
+        <v>4.767724244292446e-24</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.470495226385538e-05</v>
+        <v>1.724689436983957e-23</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.798213533125818e-05</v>
+        <v>2.907194616037331e-24</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.535124728339724e-05</v>
+        <v>5.405406820117726e-23</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.077833000337705e-05</v>
+        <v>7.820162746907712e-24</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.785716035054065e-05</v>
+        <v>3.693531166361636e-24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.984344791912008e-05</v>
+        <v>3.534587211328818e-23</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.726986531342845e-05</v>
+        <v>8.178040540613897e-24</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.500901559367776e-05</v>
+        <v>1.427163131287343e-23</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.266141018480994e-05</v>
+        <v>2.235694914268765e-25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.000119617412565276</v>
+        <v>1.362527876126932e-22</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0001445953676011413</v>
+        <v>1.255202261343564e-23</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0001212088754982688</v>
+        <v>1.790792509853495e-23</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.909324631327763e-05</v>
+        <v>2.346712887182329e-24</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.878927913727239e-05</v>
+        <v>5.462603022278594e-24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.000133313427795656</v>
+        <v>1.558090533499056e-23</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0001305327605223283</v>
+        <v>5.520624688490686e-23</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0001304314064327627</v>
+        <v>1.768356201303742e-23</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001317513815592974</v>
+        <v>1.233028564589159e-23</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.962359915021807e-05</v>
+        <v>2.379134281526007e-24</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.245969805400819e-05</v>
+        <v>5.63387143011977e-24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.918248381116427e-05</v>
+        <v>1.16979607766763e-23</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.127007089962717e-05</v>
+        <v>5.473678234957445e-24</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0001682560687186196</v>
+        <v>2.285248000891128e-23</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0001373902050545439</v>
+        <v>5.490364615255132e-23</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.288748121121898e-05</v>
+        <v>5.83682916938458e-23</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.769126346422127e-06</v>
+        <v>2.021484784165793e-23</v>
       </c>
       <c r="BL4" t="n">
-        <v>4.357424768386409e-05</v>
+        <v>2.326548498039612e-23</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.261027450207621e-05</v>
+        <v>1.138985931722866e-23</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.815860170812812e-06</v>
+        <v>4.121723682424243e-24</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.834247374674305e-05</v>
+        <v>2.345398842129457e-24</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.394530646502972e-05</v>
+        <v>3.718412628173212e-23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.657234133745078e-05</v>
+        <v>1.136450927203938e-23</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.039975126739591e-05</v>
+        <v>3.600106842672855e-23</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.736332190688699e-05</v>
+        <v>3.031885323375412e-24</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.488900104770437e-05</v>
+        <v>8.596734776947191e-24</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.404382293112576e-05</v>
+        <v>1.112976241044643e-24</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.858527871780097e-05</v>
+        <v>2.807366635064328e-25</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001103409304050729</v>
+        <v>2.360017815209786e-23</v>
       </c>
       <c r="BX4" t="n">
-        <v>4.902040382148698e-05</v>
+        <v>3.181170268269477e-23</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.187674782471731e-05</v>
+        <v>7.689243075532871e-23</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.500368620734662e-05</v>
+        <v>1.09156134959497e-23</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.492939089890569e-05</v>
+        <v>1.638500861062225e-23</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.286045390879735e-05</v>
+        <v>4.607636756491419e-24</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.21006669360213e-05</v>
+        <v>2.136322106038074e-24</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.095470906875562e-05</v>
+        <v>8.570229050531765e-24</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.287359373236541e-05</v>
+        <v>3.009877326854149e-23</v>
       </c>
       <c r="CF4" t="n">
-        <v>4.021128188469447e-05</v>
+        <v>2.806878527379222e-24</v>
       </c>
       <c r="CG4" t="n">
-        <v>6.029144969943445e-07</v>
+        <v>5.579671558335203e-24</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.27511402752134e-05</v>
+        <v>8.294343881592441e-25</v>
       </c>
       <c r="CI4" t="n">
-        <v>6.65877087158151e-05</v>
+        <v>1.120620303216234e-23</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.935735993669368e-06</v>
+        <v>1.69260520179117e-24</v>
       </c>
       <c r="CK4" t="n">
-        <v>3.343981234138482e-06</v>
+        <v>4.440165925047977e-24</v>
       </c>
       <c r="CL4" t="n">
-        <v>4.944037573295645e-05</v>
+        <v>8.23084057872215e-24</v>
       </c>
       <c r="CM4" t="n">
-        <v>5.349754064809531e-05</v>
+        <v>1.834547784366845e-23</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0001241431746166199</v>
+        <v>8.802058231180667e-23</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.34202006040141e-05</v>
+        <v>3.76430098257428e-23</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.311474135145545e-05</v>
+        <v>2.163044769202436e-23</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.772667176031973e-05</v>
+        <v>3.110009019275662e-23</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.58332331920974e-05</v>
+        <v>3.425104046192453e-23</v>
       </c>
       <c r="CS4" t="n">
-        <v>5.583788151852787e-06</v>
+        <v>4.961785210268172e-25</v>
       </c>
       <c r="CT4" t="n">
-        <v>5.350990250008181e-05</v>
+        <v>5.08536579309738e-24</v>
       </c>
       <c r="CU4" t="n">
-        <v>9.826212044572458e-05</v>
+        <v>2.057507012997443e-25</v>
       </c>
       <c r="CV4" t="n">
-        <v>5.718983629776631e-06</v>
+        <v>6.873517038868014e-24</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.964953637274448e-05</v>
+        <v>3.001033249473535e-23</v>
       </c>
       <c r="CX4" t="n">
-        <v>3.474379991530441e-05</v>
+        <v>4.750224942831928e-24</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.005026570055634e-05</v>
+        <v>9.950059580872761e-24</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.987153518712148e-05</v>
+        <v>3.085092216495532e-24</v>
       </c>
       <c r="DA4" t="n">
-        <v>5.150616561877541e-05</v>
+        <v>5.281129909767479e-24</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.420190503471531e-05</v>
+        <v>9.292680489307651e-24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.227351640409324e-05</v>
+        <v>1.468657254345014e-24</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.533373066806234e-05</v>
+        <v>4.092761837580412e-24</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0001118334330385551</v>
+        <v>1.120266656872424e-23</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.765253495657817e-05</v>
+        <v>2.705475151735447e-23</v>
       </c>
       <c r="DG4" t="n">
-        <v>5.255251016933471e-05</v>
+        <v>1.453444505661324e-23</v>
       </c>
       <c r="DH4" t="n">
-        <v>5.533138755708933e-05</v>
+        <v>7.198425179901392e-24</v>
       </c>
       <c r="DI4" t="n">
-        <v>2.787391167657916e-05</v>
+        <v>9.166308127734866e-24</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0001259243435924873</v>
+        <v>6.770512315029686e-23</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.459053575876169e-06</v>
+        <v>6.462339069239666e-24</v>
       </c>
       <c r="DL4" t="n">
-        <v>2.913197567977477e-05</v>
+        <v>4.557071797985929e-23</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0001897062902571633</v>
+        <v>5.856954588798578e-24</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.803327414672822e-05</v>
+        <v>1.151778257934111e-23</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.800360774330329e-06</v>
+        <v>3.506686305516418e-24</v>
       </c>
       <c r="DP4" t="n">
-        <v>5.018393494538032e-06</v>
+        <v>1.616178976786774e-24</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.737859929562546e-05</v>
+        <v>2.06967266810558e-23</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.882730081590125e-06</v>
+        <v>1.9407716917872e-23</v>
       </c>
       <c r="DS4" t="n">
-        <v>7.244571861519944e-06</v>
+        <v>1.309609130229662e-23</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.237224205397069e-05</v>
+        <v>3.965879556318492e-23</v>
       </c>
       <c r="DU4" t="n">
-        <v>6.205909812706523e-07</v>
+        <v>2.712187726950154e-23</v>
       </c>
       <c r="DV4" t="n">
-        <v>5.655690256389789e-05</v>
+        <v>3.476524208805293e-24</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.398826083866879e-05</v>
+        <v>1.28506230321408e-25</v>
       </c>
       <c r="DX4" t="n">
-        <v>5.194473487790674e-06</v>
+        <v>5.123153965951458e-23</v>
       </c>
       <c r="DY4" t="n">
-        <v>1.446781607228331e-05</v>
+        <v>2.250259810934042e-23</v>
       </c>
       <c r="DZ4" t="n">
-        <v>7.492294389521703e-05</v>
+        <v>4.997279533382049e-23</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.947482451214455e-05</v>
+        <v>7.206438428976627e-24</v>
       </c>
       <c r="EB4" t="n">
-        <v>3.493225676720613e-06</v>
+        <v>7.089576574477187e-24</v>
       </c>
       <c r="EC4" t="n">
-        <v>7.758103492960799e-06</v>
+        <v>1.131850290404689e-23</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.218666410655715e-05</v>
+        <v>1.136255920788167e-23</v>
       </c>
       <c r="EE4" t="n">
-        <v>2.526229036448058e-05</v>
+        <v>2.462721509726682e-23</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.166725269285962e-05</v>
+        <v>6.88397970105396e-24</v>
       </c>
       <c r="EG4" t="n">
-        <v>3.992057827417739e-05</v>
+        <v>1.830083462732019e-23</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.298303843417671e-05</v>
+        <v>1.268860283512199e-24</v>
       </c>
       <c r="EI4" t="n">
-        <v>5.143699672771618e-05</v>
+        <v>1.008510862354207e-23</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.403155278647318e-05</v>
+        <v>4.982346475332305e-24</v>
       </c>
       <c r="EK4" t="n">
-        <v>2.115142251568614e-06</v>
+        <v>2.246599496333816e-23</v>
       </c>
       <c r="EL4" t="n">
-        <v>3.668866338557564e-05</v>
+        <v>1.318837856187661e-23</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.827381674956996e-05</v>
+        <v>1.789256913215392e-23</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.027600137604168e-05</v>
+        <v>2.41579154338636e-23</v>
       </c>
       <c r="EO4" t="n">
-        <v>4.535282278084196e-05</v>
+        <v>3.045978126231959e-24</v>
       </c>
       <c r="EP4" t="n">
-        <v>7.240105333039537e-07</v>
+        <v>5.046908035106951e-24</v>
       </c>
       <c r="EQ4" t="n">
-        <v>7.277963959495537e-06</v>
+        <v>8.474374561938359e-24</v>
       </c>
       <c r="ER4" t="n">
-        <v>4.308341158321127e-05</v>
+        <v>3.376072633286712e-24</v>
       </c>
       <c r="ES4" t="n">
-        <v>2.926086017396301e-05</v>
+        <v>2.10358706059848e-23</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001211553608300164</v>
+        <v>1.27551771734963e-23</v>
       </c>
       <c r="EU4" t="n">
-        <v>7.091653242241591e-05</v>
+        <v>2.368948903948246e-24</v>
       </c>
       <c r="EV4" t="n">
-        <v>7.128521974664181e-05</v>
+        <v>1.524330599971398e-23</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0001103777904063463</v>
+        <v>6.712262825788166e-24</v>
       </c>
       <c r="EX4" t="n">
-        <v>7.248175734275719e-06</v>
+        <v>1.00449224713083e-23</v>
       </c>
       <c r="EY4" t="n">
-        <v>3.471634408924729e-05</v>
+        <v>3.32221954475608e-23</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.850666194513906e-05</v>
+        <v>7.634894621796805e-25</v>
       </c>
       <c r="FA4" t="n">
-        <v>5.79960487812059e-06</v>
+        <v>5.735865228708058e-24</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.674731695151422e-05</v>
+        <v>6.869596400169066e-24</v>
       </c>
       <c r="FC4" t="n">
-        <v>3.424554961384274e-05</v>
+        <v>1.255735767973765e-23</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.379937384626828e-05</v>
+        <v>3.153834541852623e-24</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.796468152155285e-06</v>
+        <v>4.132074720792101e-24</v>
       </c>
       <c r="FF4" t="n">
-        <v>6.565441435668617e-05</v>
+        <v>4.510559927925374e-24</v>
       </c>
       <c r="FG4" t="n">
-        <v>6.644046516157687e-05</v>
+        <v>1.83759152528355e-24</v>
       </c>
       <c r="FH4" t="n">
-        <v>4.130004890612327e-05</v>
+        <v>4.921505972447587e-24</v>
       </c>
       <c r="FI4" t="n">
-        <v>4.920159699395299e-05</v>
+        <v>1.220811475750002e-23</v>
       </c>
       <c r="FJ4" t="n">
-        <v>7.525077671743929e-05</v>
+        <v>9.475350698242439e-24</v>
       </c>
       <c r="FK4" t="n">
-        <v>6.793008651584387e-05</v>
+        <v>2.726571501151592e-25</v>
       </c>
       <c r="FL4" t="n">
-        <v>5.586647603195161e-05</v>
+        <v>1.606972457263257e-23</v>
       </c>
       <c r="FM4" t="n">
-        <v>3.333709901198745e-05</v>
+        <v>2.093308676319993e-23</v>
       </c>
       <c r="FN4" t="n">
-        <v>8.501250704284757e-05</v>
+        <v>2.739058222648154e-23</v>
       </c>
       <c r="FO4" t="n">
-        <v>6.292908074101433e-05</v>
+        <v>2.304560578028387e-23</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.23556957684923e-05</v>
+        <v>1.849079548874103e-23</v>
       </c>
       <c r="FQ4" t="n">
-        <v>1.376858926960267e-05</v>
+        <v>8.875342304870432e-24</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.025265247444622e-05</v>
+        <v>2.321557690636641e-23</v>
       </c>
       <c r="FS4" t="n">
-        <v>8.529521437594667e-05</v>
+        <v>6.080727921883364e-23</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001998960215132684</v>
+        <v>2.89975613101764e-23</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0001770274684531614</v>
+        <v>2.366169194776519e-23</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.271221455885097e-05</v>
+        <v>4.597626506034617e-23</v>
       </c>
       <c r="FW4" t="n">
-        <v>5.76090496906545e-06</v>
+        <v>5.296928979318974e-23</v>
       </c>
       <c r="FX4" t="n">
-        <v>7.281008583959192e-05</v>
+        <v>3.554969799397919e-23</v>
       </c>
       <c r="FY4" t="n">
-        <v>8.114497177302837e-05</v>
+        <v>9.240269359625672e-24</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.389658609696198e-05</v>
+        <v>1.98712563189453e-23</v>
       </c>
       <c r="GA4" t="n">
-        <v>3.427525007282384e-05</v>
+        <v>1.239668564600586e-23</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001081014124793001</v>
+        <v>2.450544652793691e-23</v>
       </c>
       <c r="GC4" t="n">
-        <v>3.728382580447942e-05</v>
+        <v>8.030382345235533e-24</v>
       </c>
       <c r="GD4" t="n">
-        <v>7.043000368867069e-05</v>
+        <v>4.633532298996657e-24</v>
       </c>
       <c r="GE4" t="n">
-        <v>5.582413723459467e-05</v>
+        <v>1.074378381357446e-23</v>
       </c>
       <c r="GF4" t="n">
-        <v>8.741422789171338e-05</v>
+        <v>1.380234427124469e-23</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0001079697758541442</v>
+        <v>2.93851602273477e-23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0002710252010729164</v>
+        <v>2.722752299177955e-07</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001587142352946103</v>
+        <v>3.775869799937936e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>1.525630796095356e-05</v>
+        <v>4.77741707527457e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0005751426797360182</v>
+        <v>1.84583984719211e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001350770180579275</v>
+        <v>1.616735971765593e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0005274597206152976</v>
+        <v>2.361756060054176e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>8.624917245469987e-05</v>
+        <v>3.505265908643196e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002268136158818379</v>
+        <v>2.971772801174666e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000520895526278764</v>
+        <v>1.900028223644767e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002022097469307482</v>
+        <v>3.430008632676618e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001452778815291822</v>
+        <v>4.066156179760583e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.236397995147854e-05</v>
+        <v>7.364563998635276e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000638553814496845</v>
+        <v>2.92558297587675e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001140558233601041</v>
+        <v>1.135811771746376e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>9.899576980387792e-05</v>
+        <v>1.646608325245325e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001623739954084158</v>
+        <v>7.473438472516136e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000437167618656531</v>
+        <v>3.477658765405067e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0003650826110970229</v>
+        <v>1.479462980569224e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.27502129948698e-05</v>
+        <v>2.127907521298766e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>5.847322609042749e-05</v>
+        <v>8.920815162127838e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>3.136296800221317e-05</v>
+        <v>3.236966108488559e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>5.437117579276673e-05</v>
+        <v>1.420321609657549e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004453387227840722</v>
+        <v>2.365898808420752e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>3.179476698278449e-05</v>
+        <v>1.342905193268962e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001819026510929689</v>
+        <v>2.344568201806396e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.315700036589988e-05</v>
+        <v>4.34117623626662e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001636278029764071</v>
+        <v>1.843981522142712e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001425781520083547</v>
+        <v>2.494361126537115e-07</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.311818677000701e-05</v>
+        <v>5.454013489725185e-07</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.463279815856367e-05</v>
+        <v>1.998364069777381e-07</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.996222509769723e-05</v>
+        <v>5.009394499211339e-08</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.21083556022495e-05</v>
+        <v>1.473667623486108e-07</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0001117658102884889</v>
+        <v>1.480168378975577e-07</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001963465329026803</v>
+        <v>2.72688509994623e-07</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0002266656956635416</v>
+        <v>2.734603867793339e-07</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001015313318930566</v>
+        <v>5.501883606484625e-07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.611099287401885e-05</v>
+        <v>6.556288667525223e-08</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0003358818066772074</v>
+        <v>1.219490059156669e-06</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001561423705425113</v>
+        <v>4.80579558370664e-07</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.4458825616166e-05</v>
+        <v>1.651617026254826e-06</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001831078407121822</v>
+        <v>4.919551770399266e-07</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0002006036520469934</v>
+        <v>4.875050194641517e-07</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.764748493675143e-05</v>
+        <v>4.272237674740609e-08</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.00014783043297939</v>
+        <v>1.141394591286371e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.015696221264079e-05</v>
+        <v>5.48110335785168e-07</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.880174310528673e-05</v>
+        <v>2.660803772869258e-07</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0006939855520613492</v>
+        <v>2.239474270027131e-06</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.164815668947995e-06</v>
+        <v>3.182412200430917e-08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0004485802492126822</v>
+        <v>1.196409357362427e-06</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0002063954307232052</v>
+        <v>9.171068882096733e-07</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0003062353935092688</v>
+        <v>6.891887096571736e-07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0005343413213267922</v>
+        <v>3.618695529894467e-07</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0005440695094875991</v>
+        <v>8.965254778559029e-07</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.679005724028684e-05</v>
+        <v>6.127168603597966e-07</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.051439464092255e-05</v>
+        <v>9.909868481372541e-08</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0001636679371586069</v>
+        <v>4.832531885767821e-07</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.02667501475662e-06</v>
+        <v>5.444052249004017e-07</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0002662683837115765</v>
+        <v>1.209646597999381e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0003797714889515191</v>
+        <v>7.65163008509262e-07</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001919915375765413</v>
+        <v>3.731479978341667e-07</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0003564506187103689</v>
+        <v>1.023582740344864e-06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.937063441611826e-05</v>
+        <v>1.164242348750122e-06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0006837645778432488</v>
+        <v>4.735179288672953e-07</v>
       </c>
       <c r="BL5" t="n">
-        <v>3.642437513917685e-05</v>
+        <v>3.518944424740766e-08</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0005403381655924022</v>
+        <v>3.699169326409901e-07</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0003311754262540489</v>
+        <v>3.932990182420326e-07</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0002107749751303345</v>
+        <v>3.024341026502952e-07</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0002263649948872626</v>
+        <v>1.64048753958923e-06</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0001167963346233591</v>
+        <v>2.129646077264624e-07</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0001813526469049975</v>
+        <v>4.1303431430606e-07</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.000235538900597021</v>
+        <v>5.19979380442237e-07</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.150025728857145e-05</v>
+        <v>5.170199415260868e-07</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0001449453120585531</v>
+        <v>3.423983230277372e-07</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0006281616515479982</v>
+        <v>6.650271302532929e-07</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.046376200974919e-05</v>
+        <v>2.677950590168621e-07</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0002984135935548693</v>
+        <v>2.410586148471339e-06</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.931298538693227e-05</v>
+        <v>1.775669716153061e-06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0002510636113584042</v>
+        <v>1.288299472435028e-06</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0003643320233095437</v>
+        <v>5.060849161964143e-08</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0003360003465786576</v>
+        <v>7.13369217919535e-07</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.152198067051359e-05</v>
+        <v>1.813991048038588e-06</v>
       </c>
       <c r="CD5" t="n">
-        <v>8.454238559352234e-05</v>
+        <v>2.343712424135447e-07</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0001704675960354507</v>
+        <v>1.473424617870478e-06</v>
       </c>
       <c r="CF5" t="n">
-        <v>6.124444189481437e-05</v>
+        <v>2.986923561820731e-07</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0001303572789765894</v>
+        <v>5.181747155802441e-07</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.871273894328624e-05</v>
+        <v>4.532836612725077e-07</v>
       </c>
       <c r="CI5" t="n">
-        <v>3.448616917012259e-05</v>
+        <v>3.127510694866942e-07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0001828882814152166</v>
+        <v>2.372773764136582e-07</v>
       </c>
       <c r="CK5" t="n">
-        <v>9.036327537614852e-05</v>
+        <v>6.930037699248714e-08</v>
       </c>
       <c r="CL5" t="n">
-        <v>5.255641735857353e-05</v>
+        <v>4.424812232173281e-07</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0001937567867571488</v>
+        <v>6.891803536746011e-07</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0002730499254539609</v>
+        <v>1.576727527208277e-06</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001206819651997648</v>
+        <v>1.249959041160764e-06</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.960137888090685e-05</v>
+        <v>9.385755674884422e-07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.000216469110455364</v>
+        <v>1.300235936696481e-07</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0002781782823149115</v>
+        <v>2.133162979589542e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0004617147205863148</v>
+        <v>1.180806776801546e-07</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001851087727118284</v>
+        <v>1.04967011793633e-06</v>
       </c>
       <c r="CU5" t="n">
-        <v>2.902475353039335e-05</v>
+        <v>3.209910630630475e-07</v>
       </c>
       <c r="CV5" t="n">
-        <v>7.518168422393501e-05</v>
+        <v>1.991971885217936e-07</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0002764174714684486</v>
+        <v>1.356218263026676e-06</v>
       </c>
       <c r="CX5" t="n">
-        <v>6.712350295856595e-05</v>
+        <v>3.645711217359349e-07</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001318930590059608</v>
+        <v>6.736559043929446e-07</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.3571614039829e-05</v>
+        <v>5.061747287982143e-07</v>
       </c>
       <c r="DA5" t="n">
-        <v>9.695937478682026e-05</v>
+        <v>3.723126837940072e-07</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001582731492817402</v>
+        <v>3.563287407359894e-07</v>
       </c>
       <c r="DC5" t="n">
-        <v>3.231058872188441e-05</v>
+        <v>2.355049559810141e-07</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.422717807348818e-05</v>
+        <v>4.609734958194167e-07</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0001668159093242139</v>
+        <v>7.326488571379741e-07</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0001632589701330289</v>
+        <v>5.722648097616911e-07</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001756091078277677</v>
+        <v>8.00347095264442e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0002248427044833079</v>
+        <v>3.136252360036451e-07</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0001627380697755143</v>
+        <v>4.487619662540965e-07</v>
       </c>
       <c r="DJ5" t="n">
-        <v>5.65969712624792e-05</v>
+        <v>6.231609290807683e-07</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0001463261578464881</v>
+        <v>3.201581080247706e-07</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002550732751842588</v>
+        <v>2.107930640704581e-06</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001092542515834793</v>
+        <v>4.326976181801001e-07</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001190875700558536</v>
+        <v>2.124473894582479e-07</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0004627735179383308</v>
+        <v>4.632927357306471e-07</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0003672325983643532</v>
+        <v>1.709531147753296e-07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0001993137848330662</v>
+        <v>1.227765437761263e-06</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.163722719065845e-05</v>
+        <v>2.04928454650144e-07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0002216939901700243</v>
+        <v>4.516389253694797e-07</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001291457156185061</v>
+        <v>3.669570673991984e-07</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002292385033797473</v>
+        <v>5.203800697017869e-07</v>
       </c>
       <c r="DV5" t="n">
-        <v>8.108450856525451e-05</v>
+        <v>3.28725178633249e-07</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.841859557316639e-06</v>
+        <v>1.370708986314639e-07</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0004944895044900477</v>
+        <v>1.199480379909801e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.279093890450895e-07</v>
+        <v>3.019828227479593e-07</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002009936724789441</v>
+        <v>1.039561311699799e-06</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0005592175293713808</v>
+        <v>3.114856994557158e-08</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.403129135724157e-05</v>
+        <v>1.80011727479723e-06</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.473727701930329e-05</v>
+        <v>5.780069614047534e-07</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0001872877037385479</v>
+        <v>1.734784518703236e-06</v>
       </c>
       <c r="EE5" t="n">
-        <v>2.258930362586398e-05</v>
+        <v>1.065325818672136e-06</v>
       </c>
       <c r="EF5" t="n">
-        <v>4.042620275868103e-05</v>
+        <v>4.978307970304741e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>1.033989246934652e-05</v>
+        <v>1.036570438373019e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002488827740307897</v>
+        <v>1.545234340483148e-07</v>
       </c>
       <c r="EI5" t="n">
-        <v>1.96023283933755e-05</v>
+        <v>7.423282681884302e-07</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.000113050831714645</v>
+        <v>3.760424078791402e-07</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001617855305084959</v>
+        <v>2.837972772340436e-07</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0001647289027459919</v>
+        <v>6.102121119511139e-08</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0001015067100524902</v>
+        <v>8.366068726672893e-08</v>
       </c>
       <c r="EN5" t="n">
-        <v>3.652365921880119e-05</v>
+        <v>1.119575827601693e-07</v>
       </c>
       <c r="EO5" t="n">
-        <v>9.921353921527043e-06</v>
+        <v>1.75982563632715e-07</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004924663226120174</v>
+        <v>7.437168960677809e-07</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001325868943240494</v>
+        <v>2.040964375282783e-07</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002188044600188732</v>
+        <v>5.168174084246857e-07</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0003830071655102074</v>
+        <v>1.043710881276638e-06</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0004603810957632959</v>
+        <v>2.39728876749723e-08</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0003938135632779449</v>
+        <v>3.516951210258412e-07</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.000358727527782321</v>
+        <v>1.441983670247282e-07</v>
       </c>
       <c r="EW5" t="n">
-        <v>8.857646025717258e-05</v>
+        <v>1.307263573835371e-06</v>
       </c>
       <c r="EX5" t="n">
-        <v>7.084896060405299e-05</v>
+        <v>1.827327480441454e-07</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.000251419231062755</v>
+        <v>1.502096552030707e-06</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.707233190652914e-06</v>
+        <v>2.284282487607925e-07</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0001682841975707561</v>
+        <v>5.189080525269674e-07</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001188483074656688</v>
+        <v>4.631084777884098e-07</v>
       </c>
       <c r="FC5" t="n">
-        <v>9.488323121331632e-05</v>
+        <v>4.470473413675791e-07</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001973278704099357</v>
+        <v>4.64347834849832e-07</v>
       </c>
       <c r="FE5" t="n">
-        <v>5.479087485582568e-05</v>
+        <v>4.841542136091448e-07</v>
       </c>
       <c r="FF5" t="n">
-        <v>7.904863741714507e-05</v>
+        <v>5.670308382832445e-07</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0001018892726278864</v>
+        <v>4.116885463645303e-07</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0002020922256633639</v>
+        <v>2.073985996275951e-07</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001208597823278978</v>
+        <v>7.179118597377965e-07</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0002839059743564576</v>
+        <v>5.250178105598025e-07</v>
       </c>
       <c r="FK5" t="n">
-        <v>8.734357106732205e-05</v>
+        <v>1.392705115677018e-07</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0001838574826251715</v>
+        <v>4.889354272563651e-07</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.000272931472864002</v>
+        <v>4.675447087265638e-07</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001490781432949007</v>
+        <v>4.414378906858474e-07</v>
       </c>
       <c r="FO5" t="n">
-        <v>7.462274516001344e-05</v>
+        <v>1.825449658099387e-07</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0001397523010382429</v>
+        <v>1.309450340158946e-06</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.000300990097457543</v>
+        <v>1.082491735360236e-06</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0002504894218873233</v>
+        <v>6.014383870933671e-07</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0002052033232757822</v>
+        <v>2.361151928198524e-06</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001321088871918619</v>
+        <v>9.063011816579092e-07</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0002720062038861215</v>
+        <v>1.424399101779272e-06</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004133103939238936</v>
+        <v>6.257734241899016e-08</v>
       </c>
       <c r="FW5" t="n">
-        <v>2.994086935359519e-05</v>
+        <v>1.212432039210398e-06</v>
       </c>
       <c r="FX5" t="n">
-        <v>8.047901792451739e-05</v>
+        <v>4.672818079143326e-07</v>
       </c>
       <c r="FY5" t="n">
-        <v>5.47548224858474e-05</v>
+        <v>1.371844859932025e-08</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.221476122736931e-05</v>
+        <v>8.096972123894375e-07</v>
       </c>
       <c r="GA5" t="n">
-        <v>2.075916563626379e-05</v>
+        <v>2.095108584398986e-07</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0002151392836822197</v>
+        <v>1.658608255183935e-07</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.000342744606314227</v>
+        <v>1.370254608445975e-06</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0001188843089039437</v>
+        <v>5.830477221024921e-07</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0003216304467059672</v>
+        <v>1.379833065584535e-06</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0002433299086987972</v>
+        <v>7.178620080594555e-07</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0001092649181373417</v>
+        <v>6.659431619482348e-07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.579004162977071e-07</v>
+        <v>3.105980661620106e-24</v>
       </c>
       <c r="B6" t="n">
-        <v>6.465545538958395e-07</v>
+        <v>3.575043075106082e-24</v>
       </c>
       <c r="C6" t="n">
-        <v>3.049190979709238e-07</v>
+        <v>2.040436457438913e-24</v>
       </c>
       <c r="D6" t="n">
-        <v>6.125216032160097e-07</v>
+        <v>2.426429253807175e-24</v>
       </c>
       <c r="E6" t="n">
-        <v>3.660411778128037e-07</v>
+        <v>5.78807283227649e-24</v>
       </c>
       <c r="F6" t="n">
-        <v>1.260444037143316e-06</v>
+        <v>4.651587747395356e-24</v>
       </c>
       <c r="G6" t="n">
-        <v>1.331902694801101e-07</v>
+        <v>1.900413252331731e-23</v>
       </c>
       <c r="H6" t="n">
-        <v>4.211323556546631e-08</v>
+        <v>1.600827704128128e-23</v>
       </c>
       <c r="I6" t="n">
-        <v>1.398820813847124e-06</v>
+        <v>3.430222412403798e-24</v>
       </c>
       <c r="J6" t="n">
-        <v>1.446074691102694e-07</v>
+        <v>3.907293144584352e-24</v>
       </c>
       <c r="K6" t="n">
-        <v>2.12254942510981e-08</v>
+        <v>1.260710167069908e-25</v>
       </c>
       <c r="L6" t="n">
-        <v>2.258529150367394e-07</v>
+        <v>4.472628340158727e-24</v>
       </c>
       <c r="M6" t="n">
-        <v>8.822171366773546e-07</v>
+        <v>6.662069972971669e-24</v>
       </c>
       <c r="N6" t="n">
-        <v>3.704353446210007e-07</v>
+        <v>1.100671746417187e-23</v>
       </c>
       <c r="O6" t="n">
-        <v>1.211342464557674e-06</v>
+        <v>1.368956713851249e-23</v>
       </c>
       <c r="P6" t="n">
-        <v>9.352018537356344e-08</v>
+        <v>2.703352800356041e-23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.952865057499366e-08</v>
+        <v>1.771638335986004e-23</v>
       </c>
       <c r="R6" t="n">
-        <v>5.831541329825995e-07</v>
+        <v>4.19368751850303e-24</v>
       </c>
       <c r="S6" t="n">
-        <v>2.343497556012153e-07</v>
+        <v>2.041181339348668e-24</v>
       </c>
       <c r="T6" t="n">
-        <v>2.072394664764943e-07</v>
+        <v>1.105947727037395e-23</v>
       </c>
       <c r="U6" t="n">
-        <v>1.295423857072819e-07</v>
+        <v>2.201511204662823e-24</v>
       </c>
       <c r="V6" t="n">
-        <v>2.775084055883781e-07</v>
+        <v>4.542227960104567e-24</v>
       </c>
       <c r="W6" t="n">
-        <v>8.122385111164476e-07</v>
+        <v>1.529289379621618e-23</v>
       </c>
       <c r="X6" t="n">
-        <v>4.445901424787735e-08</v>
+        <v>3.662016962058962e-24</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.267597037392989e-08</v>
+        <v>4.482227199653457e-24</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.316699460105156e-07</v>
+        <v>1.070126184420033e-23</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.217505692049599e-08</v>
+        <v>1.039787895625727e-24</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.697897075331639e-08</v>
+        <v>2.335382280785413e-24</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.949381953636475e-07</v>
+        <v>7.290056107208244e-24</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.043798410042655e-07</v>
+        <v>6.963389595217128e-25</v>
       </c>
       <c r="AE6" t="n">
-        <v>5.058303145233367e-07</v>
+        <v>1.591908684961518e-24</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.301592587627965e-07</v>
+        <v>7.764570141194977e-24</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.923073587155159e-08</v>
+        <v>9.422925369064166e-24</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.910413965968473e-07</v>
+        <v>8.645680440672534e-24</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.769900220300769e-07</v>
+        <v>8.325211219952834e-24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.636344677535817e-07</v>
+        <v>2.838339680786021e-24</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.27894205915436e-09</v>
+        <v>1.787801385959168e-24</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.803979626264663e-08</v>
+        <v>3.596214918510856e-24</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.525503847688015e-07</v>
+        <v>7.494835326303209e-25</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.588499393776146e-07</v>
+        <v>5.960070542024543e-24</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.483030693336332e-07</v>
+        <v>3.271309538490646e-24</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.123312441426606e-07</v>
+        <v>2.977014377479534e-25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.183563824724843e-08</v>
+        <v>3.635945109141407e-24</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.265342568032793e-08</v>
+        <v>4.266800724920724e-25</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.713206180895213e-08</v>
+        <v>1.200328978447255e-24</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.109736716553016e-09</v>
+        <v>2.228777392990882e-24</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.190831302570587e-07</v>
+        <v>2.094341453017109e-23</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.493411557225045e-07</v>
+        <v>4.945495232575358e-25</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.517474381937063e-07</v>
+        <v>2.395853399551261e-25</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.93621893535601e-07</v>
+        <v>9.141473208716698e-24</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.772151325800223e-07</v>
+        <v>1.174309860881214e-23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.584749480178289e-07</v>
+        <v>2.517701052186925e-24</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.283498911827337e-07</v>
+        <v>1.284077410373912e-23</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.894778721289185e-07</v>
+        <v>1.292311146072156e-24</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.481693214434927e-08</v>
+        <v>1.604681526308404e-24</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.38833144092132e-07</v>
+        <v>8.294014137734059e-24</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.886911829591554e-07</v>
+        <v>3.177422468994862e-24</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.713275873451494e-07</v>
+        <v>7.935484744920161e-24</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.732395276121679e-07</v>
+        <v>4.609500045949552e-24</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.013804246165819e-07</v>
+        <v>5.005255390450376e-24</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.8299072002701e-07</v>
+        <v>4.579302056067239e-24</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.874361998943641e-09</v>
+        <v>1.437074064156178e-23</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.15371124770536e-07</v>
+        <v>6.815649752735074e-26</v>
       </c>
       <c r="BL6" t="n">
-        <v>2.398121523583541e-08</v>
+        <v>1.596458538839994e-24</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.066028770286721e-07</v>
+        <v>7.326567745345493e-24</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.502142623621694e-07</v>
+        <v>2.754239416895635e-24</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.384223532520991e-07</v>
+        <v>2.509033245775583e-24</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.390283870250641e-07</v>
+        <v>8.548607950841467e-24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.628723052566784e-07</v>
+        <v>2.574914964275115e-24</v>
       </c>
       <c r="BR6" t="n">
-        <v>1.976305981088444e-07</v>
+        <v>8.159279061705026e-25</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.064253739168635e-07</v>
+        <v>2.84087350201359e-24</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.026457756684977e-07</v>
+        <v>6.734077985261148e-24</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.970420436871791e-09</v>
+        <v>4.221944121697594e-26</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.881606692677451e-07</v>
+        <v>5.322539190834793e-25</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.254979278859537e-07</v>
+        <v>3.397349789622334e-24</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.8340713836551e-07</v>
+        <v>6.14495113921576e-24</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.531380568550958e-07</v>
+        <v>1.408413643064231e-23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.568423269622144e-07</v>
+        <v>2.80505901970133e-24</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.323069677207968e-07</v>
+        <v>9.492974639725981e-25</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.274913744164223e-07</v>
+        <v>5.03162030519422e-24</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.804925086114963e-08</v>
+        <v>5.654057591823471e-24</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.970037537077587e-08</v>
+        <v>2.407488900688045e-24</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.288275619515389e-08</v>
+        <v>8.293150729473294e-25</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.123027786320563e-07</v>
+        <v>1.046593595870295e-24</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.188181096902554e-08</v>
+        <v>1.701288982635843e-24</v>
       </c>
       <c r="CH6" t="n">
-        <v>2.748348926218114e-08</v>
+        <v>2.757729534755559e-25</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.238639271150532e-07</v>
+        <v>1.853249033745603e-24</v>
       </c>
       <c r="CJ6" t="n">
-        <v>5.554350224201698e-08</v>
+        <v>1.885420950828005e-24</v>
       </c>
       <c r="CK6" t="n">
-        <v>9.527015265575756e-08</v>
+        <v>1.340291934302801e-25</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.840019692167516e-08</v>
+        <v>4.161186449207924e-24</v>
       </c>
       <c r="CM6" t="n">
-        <v>4.265590547447573e-08</v>
+        <v>6.279066565003742e-25</v>
       </c>
       <c r="CN6" t="n">
-        <v>3.655166551652655e-07</v>
+        <v>1.444049803368866e-23</v>
       </c>
       <c r="CO6" t="n">
-        <v>3.932337477863257e-08</v>
+        <v>7.442480600175953e-25</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.878958926226915e-07</v>
+        <v>1.166960063548793e-24</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.003194481403625e-07</v>
+        <v>5.644247712036595e-24</v>
       </c>
       <c r="CR6" t="n">
-        <v>2.772103755432909e-07</v>
+        <v>1.157120305655132e-24</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.440835314449942e-07</v>
+        <v>1.249704768581169e-23</v>
       </c>
       <c r="CT6" t="n">
-        <v>4.227857175465033e-07</v>
+        <v>4.15250700709823e-24</v>
       </c>
       <c r="CU6" t="n">
-        <v>4.099852617400757e-07</v>
+        <v>3.387484590964479e-25</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.803771081971718e-08</v>
+        <v>1.578726424804823e-24</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.001655380861166e-08</v>
+        <v>7.237385639503674e-25</v>
       </c>
       <c r="CX6" t="n">
-        <v>9.441411918942322e-08</v>
+        <v>2.607650719689524e-25</v>
       </c>
       <c r="CY6" t="n">
-        <v>3.560271011338045e-08</v>
+        <v>2.421641262542936e-24</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.372088576090391e-07</v>
+        <v>2.022403886006466e-24</v>
       </c>
       <c r="DA6" t="n">
-        <v>8.881805513283325e-08</v>
+        <v>3.177839973628951e-24</v>
       </c>
       <c r="DB6" t="n">
-        <v>4.503080219819822e-08</v>
+        <v>2.88410958772217e-24</v>
       </c>
       <c r="DC6" t="n">
-        <v>6.475140423845005e-08</v>
+        <v>5.862896584959542e-25</v>
       </c>
       <c r="DD6" t="n">
-        <v>5.13775262334093e-08</v>
+        <v>2.91636275747781e-24</v>
       </c>
       <c r="DE6" t="n">
-        <v>3.357563684858178e-07</v>
+        <v>5.350665237549543e-24</v>
       </c>
       <c r="DF6" t="n">
-        <v>5.054171765550564e-07</v>
+        <v>1.27359723547587e-23</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.736611920932774e-07</v>
+        <v>1.061562941521678e-23</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.533910563011887e-07</v>
+        <v>5.160036605372433e-24</v>
       </c>
       <c r="DI6" t="n">
-        <v>7.609224894622457e-08</v>
+        <v>7.131624438447277e-24</v>
       </c>
       <c r="DJ6" t="n">
-        <v>7.361454095189401e-07</v>
+        <v>2.331251213439997e-23</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.389166636225127e-08</v>
+        <v>1.332719954296424e-24</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.435780857013015e-07</v>
+        <v>1.132373936273575e-24</v>
       </c>
       <c r="DM6" t="n">
-        <v>9.008066399474046e-07</v>
+        <v>1.715903025335515e-24</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.362716943731357e-07</v>
+        <v>4.741360118409507e-24</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.888114979919919e-07</v>
+        <v>2.092555905801186e-24</v>
       </c>
       <c r="DP6" t="n">
-        <v>6.516208372886467e-08</v>
+        <v>2.502301895671332e-24</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.224514392106357e-07</v>
+        <v>1.470441302725216e-23</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.851960149679144e-07</v>
+        <v>1.262469721319003e-24</v>
       </c>
       <c r="DS6" t="n">
-        <v>5.618480969360462e-08</v>
+        <v>2.748724884737687e-24</v>
       </c>
       <c r="DT6" t="n">
-        <v>3.556721139830188e-09</v>
+        <v>9.246906046421296e-24</v>
       </c>
       <c r="DU6" t="n">
-        <v>2.706443069655506e-09</v>
+        <v>7.375883384835385e-24</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.811830424638174e-07</v>
+        <v>2.868832704646886e-24</v>
       </c>
       <c r="DW6" t="n">
-        <v>8.18336829411237e-08</v>
+        <v>2.337229595810214e-24</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.848384414415705e-07</v>
+        <v>8.497033802579928e-24</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.205435833957381e-07</v>
+        <v>1.833155760413492e-24</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.514189591489412e-07</v>
+        <v>1.273706177166881e-23</v>
       </c>
       <c r="EA6" t="n">
-        <v>4.468594738682441e-07</v>
+        <v>3.028063785327682e-25</v>
       </c>
       <c r="EB6" t="n">
-        <v>5.072072895018209e-07</v>
+        <v>9.349463486126364e-24</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.875312077321723e-07</v>
+        <v>7.643415305649323e-25</v>
       </c>
       <c r="ED6" t="n">
-        <v>2.097376778920079e-07</v>
+        <v>2.391093610064384e-25</v>
       </c>
       <c r="EE6" t="n">
-        <v>4.923971985704156e-08</v>
+        <v>2.962125367450586e-24</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.141703158211385e-08</v>
+        <v>3.30092313035361e-25</v>
       </c>
       <c r="EG6" t="n">
-        <v>7.958222880688481e-08</v>
+        <v>1.973927200089277e-24</v>
       </c>
       <c r="EH6" t="n">
-        <v>5.37510622677928e-08</v>
+        <v>1.277545839293908e-24</v>
       </c>
       <c r="EI6" t="n">
-        <v>4.525886083683872e-07</v>
+        <v>4.003804359881354e-24</v>
       </c>
       <c r="EJ6" t="n">
-        <v>1.218172087646963e-07</v>
+        <v>3.318260567417138e-24</v>
       </c>
       <c r="EK6" t="n">
-        <v>5.000849512271088e-09</v>
+        <v>8.725690312857929e-26</v>
       </c>
       <c r="EL6" t="n">
-        <v>2.646554548846325e-07</v>
+        <v>1.172179660335801e-24</v>
       </c>
       <c r="EM6" t="n">
-        <v>3.995476447471447e-07</v>
+        <v>1.688039077656524e-24</v>
       </c>
       <c r="EN6" t="n">
-        <v>1.213385871778883e-07</v>
+        <v>7.927553537379069e-24</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.352759113615321e-07</v>
+        <v>6.440807110831659e-24</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.792593593563652e-07</v>
+        <v>4.96338344246215e-24</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1.3775195384369e-07</v>
+        <v>3.386530562307227e-25</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.651277952736564e-08</v>
+        <v>8.118680335217826e-26</v>
       </c>
       <c r="ES6" t="n">
-        <v>3.898065585872246e-07</v>
+        <v>9.319045009621042e-24</v>
       </c>
       <c r="ET6" t="n">
-        <v>5.596905339189107e-07</v>
+        <v>3.500936692808715e-24</v>
       </c>
       <c r="EU6" t="n">
-        <v>3.480910208963905e-07</v>
+        <v>7.252696443597882e-25</v>
       </c>
       <c r="EV6" t="n">
-        <v>5.673435907738167e-07</v>
+        <v>5.79953182578573e-25</v>
       </c>
       <c r="EW6" t="n">
-        <v>6.957881737434946e-08</v>
+        <v>6.520949067914872e-25</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.762795148214536e-08</v>
+        <v>1.522649951534347e-24</v>
       </c>
       <c r="EY6" t="n">
-        <v>4.398475361711007e-09</v>
+        <v>1.534396090413088e-24</v>
       </c>
       <c r="EZ6" t="n">
-        <v>5.887687226646676e-09</v>
+        <v>3.087014867736782e-25</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.111939695874753e-08</v>
+        <v>1.257278227701744e-24</v>
       </c>
       <c r="FB6" t="n">
-        <v>1.359717174409525e-07</v>
+        <v>2.29188961806741e-24</v>
       </c>
       <c r="FC6" t="n">
-        <v>4.533324116096082e-08</v>
+        <v>2.49348992492956e-24</v>
       </c>
       <c r="FD6" t="n">
-        <v>2.783917807391845e-08</v>
+        <v>2.570216114293167e-24</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.220335548168805e-07</v>
+        <v>1.086095016838332e-24</v>
       </c>
       <c r="FF6" t="n">
-        <v>8.712407861821703e-08</v>
+        <v>2.745796435842281e-24</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.333198156316939e-07</v>
+        <v>8.840680545555926e-24</v>
       </c>
       <c r="FH6" t="n">
-        <v>1.618569598349495e-07</v>
+        <v>2.089254128482384e-24</v>
       </c>
       <c r="FI6" t="n">
-        <v>4.379273477184142e-08</v>
+        <v>1.632016838573283e-24</v>
       </c>
       <c r="FJ6" t="n">
-        <v>4.122923087379604e-07</v>
+        <v>4.144986007227853e-24</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.532207474814641e-07</v>
+        <v>5.124753618095065e-24</v>
       </c>
       <c r="FL6" t="n">
-        <v>6.179622005220153e-07</v>
+        <v>4.756229357612018e-24</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.989960989907559e-08</v>
+        <v>1.708083047182059e-25</v>
       </c>
       <c r="FN6" t="n">
-        <v>1.767346020642435e-07</v>
+        <v>5.580205222737585e-24</v>
       </c>
       <c r="FO6" t="n">
-        <v>2.073918636824601e-07</v>
+        <v>4.580320081065426e-24</v>
       </c>
       <c r="FP6" t="n">
-        <v>3.158251047352678e-07</v>
+        <v>1.133868038828063e-24</v>
       </c>
       <c r="FQ6" t="n">
-        <v>3.245132518259197e-07</v>
+        <v>1.112888677484163e-23</v>
       </c>
       <c r="FR6" t="n">
-        <v>3.199347009541498e-09</v>
+        <v>5.488123461423399e-24</v>
       </c>
       <c r="FS6" t="n">
-        <v>7.437556348577345e-09</v>
+        <v>6.687491804503321e-24</v>
       </c>
       <c r="FT6" t="n">
-        <v>1.493748527536809e-06</v>
+        <v>1.548446590603593e-24</v>
       </c>
       <c r="FU6" t="n">
-        <v>6.24594463261019e-07</v>
+        <v>2.725350738900762e-25</v>
       </c>
       <c r="FV6" t="n">
-        <v>4.333057574967825e-07</v>
+        <v>1.418957242379053e-23</v>
       </c>
       <c r="FW6" t="n">
-        <v>4.964658018025148e-08</v>
+        <v>3.411460933494927e-24</v>
       </c>
       <c r="FX6" t="n">
-        <v>1.529864448457374e-07</v>
+        <v>3.087402395656472e-24</v>
       </c>
       <c r="FY6" t="n">
-        <v>2.802809149216046e-07</v>
+        <v>2.232281513131874e-24</v>
       </c>
       <c r="FZ6" t="n">
-        <v>6.07022627718834e-08</v>
+        <v>1.907952001572475e-24</v>
       </c>
       <c r="GA6" t="n">
-        <v>3.210043644230609e-07</v>
+        <v>8.36280714740431e-25</v>
       </c>
       <c r="GB6" t="n">
-        <v>3.556067440513289e-07</v>
+        <v>9.71908426326767e-24</v>
       </c>
       <c r="GC6" t="n">
-        <v>1.874076929198054e-07</v>
+        <v>3.449619713202278e-24</v>
       </c>
       <c r="GD6" t="n">
-        <v>6.408677108993288e-07</v>
+        <v>6.438549785351369e-24</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.733797543896799e-07</v>
+        <v>3.28107149497753e-24</v>
       </c>
       <c r="GF6" t="n">
-        <v>3.595135922296322e-07</v>
+        <v>7.339036480813417e-24</v>
       </c>
       <c r="GG6" t="n">
-        <v>8.527033514837967e-07</v>
+        <v>1.053011610422992e-23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.01582804240752e-06</v>
+        <v>1.134737080519953e-37</v>
       </c>
       <c r="B7" t="n">
-        <v>4.511541646934347e-06</v>
+        <v>2.028698126329022e-37</v>
       </c>
       <c r="C7" t="n">
-        <v>1.586328039593354e-06</v>
+        <v>2.193985203831834e-37</v>
       </c>
       <c r="D7" t="n">
-        <v>2.364579813729506e-06</v>
+        <v>2.999002697201646e-37</v>
       </c>
       <c r="E7" t="n">
-        <v>5.16298405273119e-06</v>
+        <v>1.297547867454518e-38</v>
       </c>
       <c r="F7" t="n">
-        <v>1.435465264876257e-06</v>
+        <v>2.797198902757301e-37</v>
       </c>
       <c r="G7" t="n">
-        <v>2.479720933479257e-06</v>
+        <v>1.230868173042424e-37</v>
       </c>
       <c r="H7" t="n">
-        <v>3.993191512563499e-06</v>
+        <v>2.412918470704086e-37</v>
       </c>
       <c r="I7" t="n">
-        <v>5.485226665769005e-06</v>
+        <v>5.671438280382374e-37</v>
       </c>
       <c r="J7" t="n">
-        <v>2.010074240388349e-06</v>
+        <v>1.240045220633349e-37</v>
       </c>
       <c r="K7" t="n">
-        <v>3.022455302925664e-06</v>
+        <v>3.599103047251015e-37</v>
       </c>
       <c r="L7" t="n">
-        <v>1.824949436013412e-06</v>
+        <v>1.360521687947859e-37</v>
       </c>
       <c r="M7" t="n">
-        <v>2.550352746766293e-06</v>
+        <v>4.823699344678752e-37</v>
       </c>
       <c r="N7" t="n">
-        <v>6.247311375773279e-06</v>
+        <v>1.408978700948089e-37</v>
       </c>
       <c r="O7" t="n">
-        <v>1.171396206700592e-06</v>
+        <v>4.808072961035619e-37</v>
       </c>
       <c r="P7" t="n">
-        <v>5.771405540144769e-07</v>
+        <v>2.216961341868412e-37</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.782807536685141e-06</v>
+        <v>2.745682014430372e-37</v>
       </c>
       <c r="R7" t="n">
-        <v>2.055799768641009e-06</v>
+        <v>5.115238032831128e-37</v>
       </c>
       <c r="S7" t="n">
-        <v>1.974637484636332e-07</v>
+        <v>2.861959518922502e-37</v>
       </c>
       <c r="T7" t="n">
-        <v>6.41976782844722e-07</v>
+        <v>4.589031401818044e-37</v>
       </c>
       <c r="U7" t="n">
-        <v>8.254708063759608e-07</v>
+        <v>1.37187455969031e-37</v>
       </c>
       <c r="V7" t="n">
-        <v>1.700847974461794e-06</v>
+        <v>4.587073619707567e-37</v>
       </c>
       <c r="W7" t="n">
-        <v>6.376557848852826e-06</v>
+        <v>7.645033315354566e-37</v>
       </c>
       <c r="X7" t="n">
-        <v>1.570771246406366e-07</v>
+        <v>3.914257538162963e-37</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.967753059441748e-07</v>
+        <v>7.120268788617089e-38</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.816176672444271e-07</v>
+        <v>3.381461441251239e-37</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.363665601023968e-07</v>
+        <v>8.002109835852396e-38</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.011903058653843e-07</v>
+        <v>6.173308280705836e-38</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.758289158715343e-08</v>
+        <v>6.658345883875828e-38</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.064927684841678e-06</v>
+        <v>3.214672620210179e-37</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.149946223857114e-06</v>
+        <v>3.424119208582829e-37</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.619828822185809e-07</v>
+        <v>1.30899695234953e-37</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.243252078595106e-06</v>
+        <v>7.668595756668618e-38</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.114859954526764e-07</v>
+        <v>1.050969812504036e-37</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.165496996691218e-06</v>
+        <v>2.576408971471757e-37</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.256613245459448e-06</v>
+        <v>8.577356868442377e-38</v>
       </c>
       <c r="AK7" t="n">
-        <v>6.012141398059612e-07</v>
+        <v>4.719019434692883e-37</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.595388994246605e-06</v>
+        <v>3.289771680133537e-37</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.620386727718142e-08</v>
+        <v>1.275609166723018e-37</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.148724196464173e-07</v>
+        <v>3.257406393970474e-37</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.788269284792477e-06</v>
+        <v>5.539805011006541e-37</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.691524630587082e-06</v>
+        <v>4.166903916113205e-39</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.864899440486624e-07</v>
+        <v>1.056192283724758e-38</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.178299044113373e-06</v>
+        <v>2.716262593950951e-37</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.796678930077178e-07</v>
+        <v>3.046284413153877e-38</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.584049869052251e-06</v>
+        <v>2.665914276439391e-37</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.882355592097156e-07</v>
+        <v>5.575702914546228e-37</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.467593441859208e-07</v>
+        <v>2.377103524033487e-37</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.528669483581325e-06</v>
+        <v>1.174629357306229e-37</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.255996373103699e-06</v>
+        <v>2.212724263727803e-37</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.721757250081282e-06</v>
+        <v>2.764679473763162e-38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.296147724540788e-06</v>
+        <v>1.19084069898031e-37</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.385236363508739e-06</v>
+        <v>1.276329546237558e-37</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.174137534893816e-06</v>
+        <v>9.307687844156728e-38</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.578034582256805e-06</v>
+        <v>1.262171050761775e-37</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.091186163648672e-07</v>
+        <v>4.392886386884274e-37</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.147947952835239e-07</v>
+        <v>1.026960861447311e-37</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.383674422570039e-06</v>
+        <v>1.823224050946916e-37</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.813710864302266e-07</v>
+        <v>2.328276904550307e-37</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.238559775629255e-06</v>
+        <v>3.477354649346406e-37</v>
       </c>
       <c r="BI7" t="n">
-        <v>7.420215979436762e-07</v>
+        <v>1.884215510554716e-37</v>
       </c>
       <c r="BJ7" t="n">
-        <v>5.130440058565e-06</v>
+        <v>1.012113039230957e-38</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.686967142537469e-06</v>
+        <v>1.66757039591889e-37</v>
       </c>
       <c r="BL7" t="n">
-        <v>4.436096787685528e-07</v>
+        <v>4.274380929937744e-37</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.439757508909679e-06</v>
+        <v>3.320000266398198e-37</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.172204633803631e-06</v>
+        <v>9.391547709975168e-38</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.991098310507368e-06</v>
+        <v>4.359174957364441e-38</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.78236007286614e-07</v>
+        <v>2.483406922368184e-37</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.163611614174442e-06</v>
+        <v>2.316019690830919e-37</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.68020687851822e-06</v>
+        <v>3.696724897131773e-37</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.806902896030806e-06</v>
+        <v>4.022913212151815e-38</v>
       </c>
       <c r="BT7" t="n">
-        <v>2.052523313977872e-06</v>
+        <v>7.635326689048004e-38</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.56421060385037e-07</v>
+        <v>3.044496916832784e-37</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.518615022177983e-06</v>
+        <v>5.161046143318274e-38</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.287091878220963e-07</v>
+        <v>3.317365376869759e-37</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.095856418942276e-06</v>
+        <v>2.981574355837268e-37</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.341107913001906e-06</v>
+        <v>5.798660486400267e-37</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.064245336441672e-06</v>
+        <v>3.86917832708502e-37</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.289060259703547e-06</v>
+        <v>6.024495988988397e-38</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.054204853469855e-06</v>
+        <v>2.26445527046008e-37</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.101076577469939e-06</v>
+        <v>3.227346636144795e-37</v>
       </c>
       <c r="CD7" t="n">
-        <v>9.065522732498721e-08</v>
+        <v>3.312799161745848e-37</v>
       </c>
       <c r="CE7" t="n">
-        <v>5.742588768953283e-07</v>
+        <v>9.25176258296491e-38</v>
       </c>
       <c r="CF7" t="n">
-        <v>4.626942882168805e-07</v>
+        <v>6.844659164576141e-39</v>
       </c>
       <c r="CG7" t="n">
-        <v>1.806928509040517e-07</v>
+        <v>2.333754972610923e-37</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.642675442781183e-06</v>
+        <v>5.59758340533952e-39</v>
       </c>
       <c r="CI7" t="n">
-        <v>8.30578557042827e-08</v>
+        <v>7.540891503978998e-38</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.118917876714477e-07</v>
+        <v>9.373759627269029e-38</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.32079946979502e-06</v>
+        <v>2.51369346633733e-38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.037673087012081e-06</v>
+        <v>2.115351732869817e-37</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.23762845305464e-06</v>
+        <v>2.701564654618341e-37</v>
       </c>
       <c r="CN7" t="n">
-        <v>3.325885700178333e-06</v>
+        <v>5.22885665756511e-38</v>
       </c>
       <c r="CO7" t="n">
-        <v>3.382109525773558e-07</v>
+        <v>6.40022222259211e-38</v>
       </c>
       <c r="CP7" t="n">
-        <v>3.327841568534495e-06</v>
+        <v>1.693008783513103e-37</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.896973685688863e-06</v>
+        <v>1.241942802961799e-37</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.724415142234648e-06</v>
+        <v>2.399958365674993e-37</v>
       </c>
       <c r="CS7" t="n">
-        <v>4.654920303437393e-06</v>
+        <v>4.417183108593632e-38</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.283430831084843e-06</v>
+        <v>2.051993087792203e-37</v>
       </c>
       <c r="CU7" t="n">
-        <v>9.011067163555708e-07</v>
+        <v>2.338008866333104e-37</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.498108469557337e-10</v>
+        <v>3.471061810306693e-37</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.19160949907382e-06</v>
+        <v>3.742578689948857e-38</v>
       </c>
       <c r="CX7" t="n">
-        <v>4.017903734165884e-07</v>
+        <v>3.805456073081883e-38</v>
       </c>
       <c r="CY7" t="n">
-        <v>5.54134771846293e-07</v>
+        <v>2.133529152341284e-37</v>
       </c>
       <c r="CZ7" t="n">
-        <v>9.177342121802212e-07</v>
+        <v>1.805366379759039e-38</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.308366475745061e-07</v>
+        <v>3.265736720977315e-38</v>
       </c>
       <c r="DB7" t="n">
-        <v>9.551258699502796e-07</v>
+        <v>3.391827798874805e-38</v>
       </c>
       <c r="DC7" t="n">
-        <v>4.764731329487404e-07</v>
+        <v>2.463572663644438e-38</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.149178612853575e-07</v>
+        <v>1.710961658918647e-37</v>
       </c>
       <c r="DE7" t="n">
-        <v>5.984663403069135e-06</v>
+        <v>2.450009607912115e-37</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.088967221425264e-06</v>
+        <v>2.475747312858308e-37</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.005193894343392e-06</v>
+        <v>5.018770068157833e-38</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.287075403728522e-06</v>
+        <v>1.717247323310222e-37</v>
       </c>
       <c r="DI7" t="n">
-        <v>5.731558303523343e-07</v>
+        <v>1.068104217502537e-37</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.97139524971135e-06</v>
+        <v>1.203099482153978e-37</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.148543217117549e-06</v>
+        <v>9.7361993093534e-39</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.029690110954107e-06</v>
+        <v>2.545044324516099e-37</v>
       </c>
       <c r="DM7" t="n">
-        <v>8.495902648064657e-07</v>
+        <v>2.468371774573119e-37</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.15567945613293e-06</v>
+        <v>1.441803164591942e-37</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.612014330021339e-06</v>
+        <v>1.861500014032502e-38</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.152008040771761e-07</v>
+        <v>1.955998313584342e-37</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.356693812544108e-06</v>
+        <v>6.496883790661236e-37</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.635226792335743e-07</v>
+        <v>1.74997537761973e-37</v>
       </c>
       <c r="DS7" t="n">
-        <v>9.90082753560273e-08</v>
+        <v>1.731115133432566e-37</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.127671218157047e-07</v>
+        <v>2.891395754983495e-37</v>
       </c>
       <c r="DU7" t="n">
-        <v>9.465446737522143e-07</v>
+        <v>2.158086403461129e-37</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.604984589675951e-07</v>
+        <v>2.026339909169379e-37</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.161551068662448e-07</v>
+        <v>2.320952037217588e-37</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.128855373622173e-07</v>
+        <v>1.677039922525289e-37</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.594469823539839e-07</v>
+        <v>2.040835388899863e-37</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.547677458001999e-07</v>
+        <v>1.845482051546498e-38</v>
       </c>
       <c r="EA7" t="n">
-        <v>3.648093525043805e-06</v>
+        <v>1.066354724395796e-37</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.100706296914723e-06</v>
+        <v>1.981251281365755e-37</v>
       </c>
       <c r="EC7" t="n">
-        <v>6.624459274462424e-07</v>
+        <v>2.088289856926776e-37</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.731454858600046e-06</v>
+        <v>2.384706408981527e-37</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.581778747095086e-06</v>
+        <v>3.259242431270371e-37</v>
       </c>
       <c r="EF7" t="n">
-        <v>2.685645767996903e-07</v>
+        <v>4.327773764544834e-37</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.61957279942726e-06</v>
+        <v>1.519903021098744e-37</v>
       </c>
       <c r="EH7" t="n">
-        <v>7.450893235727563e-09</v>
+        <v>7.814424964215202e-40</v>
       </c>
       <c r="EI7" t="n">
-        <v>8.929536079449463e-07</v>
+        <v>1.94005960853948e-38</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.228315568368998e-06</v>
+        <v>2.514040876252605e-37</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.515470498565264e-08</v>
+        <v>1.644060082907711e-37</v>
       </c>
       <c r="EL7" t="n">
-        <v>3.490627022983972e-07</v>
+        <v>3.930870604080797e-39</v>
       </c>
       <c r="EM7" t="n">
-        <v>2.628886932143359e-06</v>
+        <v>1.163353220667684e-38</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.186517917834863e-07</v>
+        <v>3.134332928238e-37</v>
       </c>
       <c r="EO7" t="n">
-        <v>2.910562955094065e-07</v>
+        <v>2.397119222882394e-37</v>
       </c>
       <c r="EP7" t="n">
-        <v>9.678652759248507e-07</v>
+        <v>1.390435934941003e-37</v>
       </c>
       <c r="EQ7" t="n">
-        <v>5.170705890122917e-07</v>
+        <v>1.858647755086276e-37</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.755739276632085e-06</v>
+        <v>1.544366553377295e-37</v>
       </c>
       <c r="ES7" t="n">
-        <v>3.199578713974915e-06</v>
+        <v>1.466800087117953e-37</v>
       </c>
       <c r="ET7" t="n">
-        <v>9.172425166070752e-07</v>
+        <v>5.090694906799803e-37</v>
       </c>
       <c r="EU7" t="n">
-        <v>9.590659146851976e-07</v>
+        <v>3.414465271098525e-37</v>
       </c>
       <c r="EV7" t="n">
-        <v>2.399702452748897e-06</v>
+        <v>2.108769665827067e-37</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.473348672538123e-07</v>
+        <v>1.403213646961979e-37</v>
       </c>
       <c r="EX7" t="n">
-        <v>4.032917786389589e-07</v>
+        <v>4.043489990905838e-37</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.411266794093535e-06</v>
+        <v>1.660248050923407e-38</v>
       </c>
       <c r="EZ7" t="n">
-        <v>6.846944415883627e-07</v>
+        <v>4.44074762382941e-38</v>
       </c>
       <c r="FA7" t="n">
-        <v>3.786219053836248e-07</v>
+        <v>2.053712537059868e-37</v>
       </c>
       <c r="FB7" t="n">
-        <v>9.802138265513349e-07</v>
+        <v>3.294631775571386e-38</v>
       </c>
       <c r="FC7" t="n">
-        <v>3.791615199588705e-08</v>
+        <v>8.749848301609976e-38</v>
       </c>
       <c r="FD7" t="n">
-        <v>7.397089802907431e-07</v>
+        <v>9.155435644969065e-38</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.175857732960139e-06</v>
+        <v>8.961684832539502e-39</v>
       </c>
       <c r="FF7" t="n">
-        <v>3.077823862440709e-08</v>
+        <v>1.796534808291509e-37</v>
       </c>
       <c r="FG7" t="n">
-        <v>4.828031592296611e-07</v>
+        <v>5.317198996911232e-37</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.816907342799823e-06</v>
+        <v>1.50481204557286e-37</v>
       </c>
       <c r="FI7" t="n">
-        <v>6.143007453829341e-07</v>
+        <v>1.839598727969999e-37</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.132389115809929e-08</v>
+        <v>2.428751573896676e-37</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.403329861204838e-06</v>
+        <v>1.637991003206782e-37</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.675649056982365e-06</v>
+        <v>3.699256875300992e-37</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.521163085271837e-06</v>
+        <v>1.865952219513355e-37</v>
       </c>
       <c r="FN7" t="n">
-        <v>6.824309366493253e-07</v>
+        <v>9.997712991882012e-38</v>
       </c>
       <c r="FO7" t="n">
-        <v>3.069684908041381e-06</v>
+        <v>2.184670044264265e-37</v>
       </c>
       <c r="FP7" t="n">
-        <v>8.906036441658216e-07</v>
+        <v>9.267108482707424e-38</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.960903091458022e-06</v>
+        <v>1.178120496248309e-37</v>
       </c>
       <c r="FR7" t="n">
-        <v>3.578398093395663e-07</v>
+        <v>2.774093845262004e-37</v>
       </c>
       <c r="FS7" t="n">
-        <v>9.625009624869563e-07</v>
+        <v>1.419742578920015e-37</v>
       </c>
       <c r="FT7" t="n">
-        <v>7.685894161113538e-06</v>
+        <v>1.468993063162683e-37</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.16145315587346e-06</v>
+        <v>5.141986914749177e-37</v>
       </c>
       <c r="FV7" t="n">
-        <v>3.207649342584773e-06</v>
+        <v>4.443548371044087e-37</v>
       </c>
       <c r="FW7" t="n">
-        <v>2.133237558155088e-06</v>
+        <v>1.536960747045277e-37</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.434781663396279e-06</v>
+        <v>7.864913747884825e-38</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.289142005589383e-06</v>
+        <v>1.673634655153102e-37</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.168380549643189e-06</v>
+        <v>3.147525760916048e-37</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.092684669856681e-06</v>
+        <v>1.263377736895374e-37</v>
       </c>
       <c r="GB7" t="n">
-        <v>2.012181084865006e-06</v>
+        <v>1.097247526132547e-38</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.278044464925188e-06</v>
+        <v>1.195062082578119e-37</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.661039270104084e-07</v>
+        <v>1.814727025474759e-37</v>
       </c>
       <c r="GE7" t="n">
-        <v>7.947382414386084e-07</v>
+        <v>3.481247344376423e-37</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.212660547229461e-06</v>
+        <v>2.602807360617909e-38</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.968440301425289e-06</v>
+        <v>3.771285634237077e-37</v>
       </c>
     </row>
     <row r="8">
@@ -4982,5123 +4982,5123 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.619552858755924e-05</v>
+        <v>2.436172508168966e-07</v>
       </c>
       <c r="B9" t="n">
-        <v>8.556163811590523e-05</v>
+        <v>5.398040229920298e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>1.06699371826835e-05</v>
+        <v>1.662354975451308e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>4.831788101000711e-05</v>
+        <v>3.473729066172382e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>6.02885993430391e-05</v>
+        <v>4.857886892750685e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>4.72170468128752e-05</v>
+        <v>2.494380169082433e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>1.111331312131369e-05</v>
+        <v>1.254473772860365e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>3.067028592340648e-05</v>
+        <v>2.342153635481736e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>3.602095966925845e-05</v>
+        <v>3.799985748287327e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.792757913994137e-05</v>
+        <v>1.552924118186638e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.905553189222701e-05</v>
+        <v>5.27957672602497e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.082129347196314e-05</v>
+        <v>2.235478632428567e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.306295548100024e-05</v>
+        <v>5.030963166063884e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>6.540032336488366e-05</v>
+        <v>1.351982518826844e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.882709329947829e-05</v>
+        <v>1.517760665592505e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07854120869888e-05</v>
+        <v>1.594632635715243e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.458133960521081e-06</v>
+        <v>2.461396206854261e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.616924055269919e-05</v>
+        <v>6.377258898737637e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.255897915252717e-07</v>
+        <v>4.717827266631502e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.198446625494398e-06</v>
+        <v>4.88577711621474e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.021604589368508e-06</v>
+        <v>5.633637556456961e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>2.966165993711911e-05</v>
+        <v>5.763447461504256e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>5.442467590910383e-05</v>
+        <v>1.254374751624709e-06</v>
       </c>
       <c r="X9" t="n">
-        <v>9.8431009973865e-06</v>
+        <v>9.864568255579798e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.802635779313277e-05</v>
+        <v>6.094580839999253e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.273428460990544e-05</v>
+        <v>2.577119460056565e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.578641786181834e-07</v>
+        <v>1.279276602872415e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.971226538444171e-06</v>
+        <v>3.135452857350174e-07</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.430340024759062e-06</v>
+        <v>5.336881372386415e-07</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.085734766093083e-05</v>
+        <v>9.000143563753227e-07</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.100036181218456e-05</v>
+        <v>7.686246590310475e-07</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.054246164741926e-05</v>
+        <v>4.044906631861522e-07</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.584173307695892e-05</v>
+        <v>1.451795696993941e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.859798612713348e-05</v>
+        <v>4.524843575381965e-07</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.135417844328913e-06</v>
+        <v>2.06420452286693e-07</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.349248683865881e-06</v>
+        <v>1.098870185956002e-07</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.799927981162909e-06</v>
+        <v>4.037972871628881e-07</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.050857918016845e-06</v>
+        <v>1.553619881633495e-06</v>
       </c>
       <c r="AM9" t="n">
-        <v>7.306965699171997e-07</v>
+        <v>1.233130205946509e-06</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.503502507053781e-07</v>
+        <v>1.601549570295902e-06</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.183842298109084e-05</v>
+        <v>6.980849889259844e-07</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.579133277118672e-05</v>
+        <v>8.062500000960426e-07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.24509388115257e-05</v>
+        <v>4.150575421135727e-07</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.784285996109247e-05</v>
+        <v>7.89324474226305e-07</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.067807872663252e-05</v>
+        <v>4.837777822785938e-08</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.05197352443065e-06</v>
+        <v>3.816185767391289e-07</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.985632636409719e-05</v>
+        <v>2.919295639003394e-06</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.359928299090825e-06</v>
+        <v>7.99395991180063e-07</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.595043952169362e-05</v>
+        <v>1.24738699014415e-06</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.032715514767915e-05</v>
+        <v>2.676478288776707e-06</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.583454938256182e-05</v>
+        <v>1.15570139769261e-06</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.687566120584961e-05</v>
+        <v>3.96103814637172e-07</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.912028452963568e-05</v>
+        <v>4.859957130065595e-07</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.9779052308877e-05</v>
+        <v>2.658530888766109e-07</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.020278745680116e-05</v>
+        <v>7.703972926265124e-08</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.040627623500768e-05</v>
+        <v>9.19027229429048e-07</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.824970114394091e-06</v>
+        <v>9.606953881302616e-07</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.282009361602832e-05</v>
+        <v>1.164860123026301e-06</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.127748302882537e-05</v>
+        <v>1.919044052556274e-06</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.592576129245572e-05</v>
+        <v>9.153768587566447e-07</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.134608985215891e-05</v>
+        <v>2.267352670060063e-07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.521847298135981e-05</v>
+        <v>5.423099196377734e-07</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.408404659741791e-05</v>
+        <v>5.165346692592721e-07</v>
       </c>
       <c r="BL9" t="n">
-        <v>6.561881036759587e-06</v>
+        <v>1.833650031812795e-07</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.123678703152109e-05</v>
+        <v>3.743374463738292e-07</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.505231577742961e-07</v>
+        <v>2.497671971468662e-07</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.801929465727881e-05</v>
+        <v>7.211273214124958e-07</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.408186997461598e-06</v>
+        <v>5.978902777314943e-07</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.283505859348224e-06</v>
+        <v>3.830247408131982e-08</v>
       </c>
       <c r="BR9" t="n">
-        <v>5.504906312125968e-06</v>
+        <v>9.803727607504698e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.169318329630187e-05</v>
+        <v>3.998271438376833e-07</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.241141247504856e-06</v>
+        <v>2.816455832999054e-07</v>
       </c>
       <c r="BU9" t="n">
-        <v>8.24615744932089e-06</v>
+        <v>4.570815690385643e-07</v>
       </c>
       <c r="BV9" t="n">
-        <v>2.048767419182695e-05</v>
+        <v>2.131286692019785e-06</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.004783012438565e-06</v>
+        <v>1.194106971524889e-06</v>
       </c>
       <c r="BX9" t="n">
-        <v>3.619145718403161e-05</v>
+        <v>3.00184410662041e-06</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.226675082463771e-05</v>
+        <v>6.702383643641951e-07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.209252655433374e-07</v>
+        <v>9.173668331641238e-07</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.5359644748969e-05</v>
+        <v>7.33865874735784e-08</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.510151352907997e-05</v>
+        <v>2.549880662172654e-07</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.543405445176177e-06</v>
+        <v>8.566603924009542e-07</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.283441856183344e-06</v>
+        <v>1.851642537076259e-07</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.26322802316281e-05</v>
+        <v>1.812620098462503e-06</v>
       </c>
       <c r="CF9" t="n">
-        <v>7.854919203964528e-06</v>
+        <v>3.55749193658994e-07</v>
       </c>
       <c r="CG9" t="n">
-        <v>9.116322871705052e-06</v>
+        <v>1.362810735372477e-06</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.01334535429487e-05</v>
+        <v>5.619376608478888e-08</v>
       </c>
       <c r="CI9" t="n">
-        <v>5.518721991393249e-06</v>
+        <v>4.028409819056833e-07</v>
       </c>
       <c r="CJ9" t="n">
-        <v>3.742933813555283e-06</v>
+        <v>8.346495405930909e-08</v>
       </c>
       <c r="CK9" t="n">
-        <v>3.363053110660985e-06</v>
+        <v>1.218477478914792e-07</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.50548999044986e-06</v>
+        <v>1.593203791117048e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.459600525777205e-06</v>
+        <v>9.044311468642263e-07</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.600883661012631e-05</v>
+        <v>2.193127784266835e-06</v>
       </c>
       <c r="CO9" t="n">
-        <v>9.280676749767736e-06</v>
+        <v>1.750368255670764e-06</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.290091950068017e-05</v>
+        <v>1.351153514406178e-06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.550705928821117e-05</v>
+        <v>4.076155732946063e-07</v>
       </c>
       <c r="CR9" t="n">
-        <v>2.062871135422029e-05</v>
+        <v>1.833881242419011e-07</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.921380655607209e-06</v>
+        <v>1.038488221638545e-06</v>
       </c>
       <c r="CT9" t="n">
-        <v>4.040499334223568e-06</v>
+        <v>5.630549821944442e-07</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.527678432466928e-05</v>
+        <v>5.111340897201444e-07</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.586289610917447e-06</v>
+        <v>2.179442333272164e-07</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.612536470929626e-05</v>
+        <v>1.712533958198037e-06</v>
       </c>
       <c r="CX9" t="n">
-        <v>4.664166226575617e-06</v>
+        <v>4.434810989550897e-07</v>
       </c>
       <c r="CY9" t="n">
-        <v>6.421968464564998e-06</v>
+        <v>1.339135224043275e-06</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.469893686589785e-05</v>
+        <v>3.550752012415614e-07</v>
       </c>
       <c r="DA9" t="n">
-        <v>6.802000825700816e-06</v>
+        <v>4.117723335639312e-07</v>
       </c>
       <c r="DB9" t="n">
-        <v>4.291701770853251e-06</v>
+        <v>2.250405373160902e-08</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.434921952954028e-06</v>
+        <v>8.615852920001998e-08</v>
       </c>
       <c r="DD9" t="n">
-        <v>8.163726761267753e-07</v>
+        <v>1.733799877001729e-07</v>
       </c>
       <c r="DE9" t="n">
-        <v>3.667782948468812e-06</v>
+        <v>9.173249964078423e-07</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.484562537574675e-05</v>
+        <v>9.091240826819558e-07</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.142589892173419e-07</v>
+        <v>4.425195641033497e-07</v>
       </c>
       <c r="DH9" t="n">
-        <v>5.147901538293809e-05</v>
+        <v>8.671873388266249e-07</v>
       </c>
       <c r="DI9" t="n">
-        <v>1.409258766216226e-05</v>
+        <v>2.546761947996856e-07</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.982817750307731e-05</v>
+        <v>2.668000206540455e-06</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.222439186676638e-05</v>
+        <v>3.73538938447382e-07</v>
       </c>
       <c r="DL9" t="n">
-        <v>1.336648529104423e-05</v>
+        <v>3.156343609589385e-06</v>
       </c>
       <c r="DM9" t="n">
-        <v>1.366456217510859e-05</v>
+        <v>3.083966362282808e-07</v>
       </c>
       <c r="DN9" t="n">
-        <v>9.720563866721932e-06</v>
+        <v>2.736117323820508e-07</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.77964502654504e-05</v>
+        <v>1.009393372441991e-06</v>
       </c>
       <c r="DP9" t="n">
-        <v>1.73540456671617e-06</v>
+        <v>4.580127779263421e-07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.523582704976434e-05</v>
+        <v>1.666272282818682e-06</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.19673404697096e-05</v>
+        <v>8.675495877241701e-08</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.548647742311005e-05</v>
+        <v>4.351559255155735e-07</v>
       </c>
       <c r="DT9" t="n">
-        <v>9.237944141204935e-06</v>
+        <v>2.738595981099934e-07</v>
       </c>
       <c r="DU9" t="n">
-        <v>9.085794772545341e-06</v>
+        <v>1.204149043587677e-06</v>
       </c>
       <c r="DV9" t="n">
-        <v>8.84748442331329e-06</v>
+        <v>1.79440246483864e-06</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.016914848150918e-05</v>
+        <v>1.178901243292785e-08</v>
       </c>
       <c r="DX9" t="n">
-        <v>7.550152076873928e-07</v>
+        <v>5.622291610052343e-08</v>
       </c>
       <c r="DY9" t="n">
-        <v>1.08501008071471e-05</v>
+        <v>6.223320951903588e-07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.158241593657294e-05</v>
+        <v>1.089070337911835e-06</v>
       </c>
       <c r="EA9" t="n">
-        <v>1.895510467875283e-05</v>
+        <v>6.149423370516161e-07</v>
       </c>
       <c r="EB9" t="n">
-        <v>8.198251634894405e-06</v>
+        <v>1.730699750623899e-06</v>
       </c>
       <c r="EC9" t="n">
-        <v>6.684818799840286e-06</v>
+        <v>2.114756370019677e-07</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.611799573060125e-06</v>
+        <v>2.955360059786472e-06</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.015829457173822e-05</v>
+        <v>1.570811718920595e-06</v>
       </c>
       <c r="EF9" t="n">
-        <v>2.472179403412156e-06</v>
+        <v>5.962235718470765e-07</v>
       </c>
       <c r="EG9" t="n">
-        <v>1.797859567886917e-06</v>
+        <v>1.18028367523948e-06</v>
       </c>
       <c r="EH9" t="n">
-        <v>9.871954716800246e-06</v>
+        <v>6.336782121252327e-07</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.048405647452455e-05</v>
+        <v>1.030644284583104e-06</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1.110121775127482e-05</v>
+        <v>1.204514035180182e-07</v>
       </c>
       <c r="EK9" t="n">
-        <v>5.556973519560415e-06</v>
+        <v>2.753548926648364e-07</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.947793058818206e-06</v>
+        <v>2.044026814473909e-07</v>
       </c>
       <c r="EM9" t="n">
-        <v>5.995576429995708e-06</v>
+        <v>2.785784545267234e-07</v>
       </c>
       <c r="EN9" t="n">
-        <v>4.875316335528623e-06</v>
+        <v>2.578823909971106e-08</v>
       </c>
       <c r="EO9" t="n">
-        <v>1.00217730505392e-05</v>
+        <v>4.938655138175818e-07</v>
       </c>
       <c r="EP9" t="n">
-        <v>1.905314820760395e-05</v>
+        <v>1.671915242695832e-06</v>
       </c>
       <c r="EQ9" t="n">
-        <v>6.120950729382457e-06</v>
+        <v>5.316645683706156e-07</v>
       </c>
       <c r="ER9" t="n">
-        <v>4.818214165425161e-06</v>
+        <v>3.952169436161057e-07</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.127659515987034e-06</v>
+        <v>3.757809849957994e-07</v>
       </c>
       <c r="ET9" t="n">
-        <v>3.719195592566393e-05</v>
+        <v>2.628452193675912e-07</v>
       </c>
       <c r="EU9" t="n">
-        <v>1.869714105851017e-05</v>
+        <v>6.565704211425327e-07</v>
       </c>
       <c r="EV9" t="n">
-        <v>2.279817181261024e-06</v>
+        <v>5.358257340049022e-07</v>
       </c>
       <c r="EW9" t="n">
-        <v>6.304126145550981e-06</v>
+        <v>1.320955902883725e-06</v>
       </c>
       <c r="EX9" t="n">
-        <v>4.370170699985465e-06</v>
+        <v>1.785526535513782e-07</v>
       </c>
       <c r="EY9" t="n">
-        <v>1.206385331897764e-05</v>
+        <v>1.947745658981148e-06</v>
       </c>
       <c r="EZ9" t="n">
-        <v>2.400199264229741e-06</v>
+        <v>3.324793738102017e-07</v>
       </c>
       <c r="FA9" t="n">
-        <v>1.068034634954529e-05</v>
+        <v>1.541360006740433e-06</v>
       </c>
       <c r="FB9" t="n">
-        <v>1.239305765921017e-05</v>
+        <v>1.55809743773716e-07</v>
       </c>
       <c r="FC9" t="n">
-        <v>8.720032383280341e-06</v>
+        <v>4.659354715386144e-07</v>
       </c>
       <c r="FD9" t="n">
-        <v>5.103548573970329e-06</v>
+        <v>1.910643447899929e-07</v>
       </c>
       <c r="FE9" t="n">
-        <v>4.74237822345458e-08</v>
+        <v>2.539890999742056e-07</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.610278094536625e-06</v>
+        <v>3.418237213281827e-07</v>
       </c>
       <c r="FG9" t="n">
-        <v>2.727000037339167e-06</v>
+        <v>5.929601343268587e-08</v>
       </c>
       <c r="FH9" t="n">
-        <v>1.086875090550166e-05</v>
+        <v>7.930455581117712e-07</v>
       </c>
       <c r="FI9" t="n">
-        <v>2.000175663852133e-05</v>
+        <v>1.617542864096322e-07</v>
       </c>
       <c r="FJ9" t="n">
-        <v>1.107805474021006e-05</v>
+        <v>1.073571098686443e-08</v>
       </c>
       <c r="FK9" t="n">
-        <v>2.016588041442446e-05</v>
+        <v>4.363910477422905e-07</v>
       </c>
       <c r="FL9" t="n">
-        <v>3.527368789946195e-06</v>
+        <v>3.380458934998387e-08</v>
       </c>
       <c r="FM9" t="n">
-        <v>2.913356865974492e-06</v>
+        <v>3.115152935606602e-08</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.225498090207111e-05</v>
+        <v>1.014196527648892e-06</v>
       </c>
       <c r="FO9" t="n">
-        <v>9.391480944032082e-07</v>
+        <v>1.23001200336148e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>1.729626455926336e-05</v>
+        <v>8.806607638689457e-07</v>
       </c>
       <c r="FQ9" t="n">
-        <v>1.262824753212044e-05</v>
+        <v>2.478452643117635e-06</v>
       </c>
       <c r="FR9" t="n">
-        <v>7.933133929327596e-06</v>
+        <v>6.308218303274771e-07</v>
       </c>
       <c r="FS9" t="n">
-        <v>2.725834065131494e-06</v>
+        <v>1.57851172843948e-06</v>
       </c>
       <c r="FT9" t="n">
-        <v>1.244010491063818e-05</v>
+        <v>1.972535301320022e-06</v>
       </c>
       <c r="FU9" t="n">
-        <v>4.732837624032982e-06</v>
+        <v>1.410636230048112e-07</v>
       </c>
       <c r="FV9" t="n">
-        <v>2.46179370151367e-05</v>
+        <v>1.056507414887164e-07</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.668468394200318e-05</v>
+        <v>1.028332349051198e-06</v>
       </c>
       <c r="FX9" t="n">
-        <v>6.049019248166587e-06</v>
+        <v>1.279285015698406e-06</v>
       </c>
       <c r="FY9" t="n">
-        <v>2.040543768089265e-05</v>
+        <v>1.490903400735988e-07</v>
       </c>
       <c r="FZ9" t="n">
-        <v>1.336196874035522e-05</v>
+        <v>6.65530592414143e-07</v>
       </c>
       <c r="GA9" t="n">
-        <v>1.702825466054492e-05</v>
+        <v>4.622160076905857e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>7.151727004384156e-06</v>
+        <v>1.156555981651763e-06</v>
       </c>
       <c r="GC9" t="n">
-        <v>2.374721952946857e-05</v>
+        <v>1.711889581201831e-06</v>
       </c>
       <c r="GD9" t="n">
-        <v>3.581517830753e-06</v>
+        <v>5.804059810543549e-07</v>
       </c>
       <c r="GE9" t="n">
-        <v>1.127648192777997e-05</v>
+        <v>1.653278104640776e-06</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.711702316242736e-05</v>
+        <v>1.082432845578296e-07</v>
       </c>
       <c r="GG9" t="n">
-        <v>1.839331707742531e-05</v>
+        <v>6.375888688125997e-07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0009384086006321013</v>
+        <v>3.364383474036003e-07</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001511333044618368</v>
+        <v>3.073202378800488e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0003298403171356767</v>
+        <v>1.25790802485426e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0004355578566901386</v>
+        <v>6.616281098104082e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002506774617359042</v>
+        <v>3.504336746118497e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0008527532918378711</v>
+        <v>1.259356849914184e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005185274640098214</v>
+        <v>7.996899853424111e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002802264643833041</v>
+        <v>1.007248556561535e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000233710918109864</v>
+        <v>1.234999444932328e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001148059847764671</v>
+        <v>6.108451771069667e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001037025009281933</v>
+        <v>1.75716161265882e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0004963952233083546</v>
+        <v>1.930557118612342e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002121302823070437</v>
+        <v>1.086148222384509e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001593772671185434</v>
+        <v>6.079771537770284e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0008898943196982145</v>
+        <v>1.107859475268924e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009732301696203649</v>
+        <v>7.224380738080072e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001549040549434721</v>
+        <v>2.703002792259213e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0003516900469549</v>
+        <v>9.436720915800834e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0004953312454745173</v>
+        <v>3.9681196994934e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>2.520776251913048e-05</v>
+        <v>1.028525048241136e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0006509422673843801</v>
+        <v>6.881876402076159e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006478654104284942</v>
+        <v>3.251150701544248e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001640750211663544</v>
+        <v>5.887548923055874e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004086257249582559</v>
+        <v>1.6468779904244e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0004516572807915509</v>
+        <v>7.089966516105051e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000474448868772015</v>
+        <v>3.13753480440937e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.000528154952917248</v>
+        <v>2.649949465194368e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0006704365951009095</v>
+        <v>4.66957999378792e-07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.588315692264587e-05</v>
+        <v>3.475448409062665e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001148105948232114</v>
+        <v>1.76181060851377e-07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0002478817477822304</v>
+        <v>1.967215439435677e-06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0003951811813749373</v>
+        <v>3.845522655865352e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.001004231860861182</v>
+        <v>9.97997972262965e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0008380981744267046</v>
+        <v>4.178688186584623e-07</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0006082895561121404</v>
+        <v>3.525341298882267e-06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0005920329713262618</v>
+        <v>2.121911393260234e-06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.000230238088988699</v>
+        <v>2.229289322031036e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.000724788464140147</v>
+        <v>2.152179149561562e-06</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.006954830198083e-05</v>
+        <v>3.5107345297547e-07</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0004930329159833491</v>
+        <v>1.937844672283973e-06</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0009531762916594744</v>
+        <v>1.270434722755454e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0006649190909229219</v>
+        <v>2.141930735888309e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0004525135736912489</v>
+        <v>1.465603077122068e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0006841649883426726</v>
+        <v>1.906517582028755e-06</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0001145797141361982</v>
+        <v>1.576908061906579e-06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001082363596651703</v>
+        <v>5.669397751262295e-07</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.227485624141991e-05</v>
+        <v>3.582482122510555e-06</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0002925545268226415</v>
+        <v>1.510552920080954e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0003667980490718037</v>
+        <v>1.772486484696856e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001931524369865656</v>
+        <v>7.965320037328638e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.001893745269626379</v>
+        <v>1.365676098430413e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0002361913793720305</v>
+        <v>1.730866188154323e-06</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0007320934673771262</v>
+        <v>5.497175607160898e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0007605515420436859</v>
+        <v>5.938828735452262e-07</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.001225136686116457</v>
+        <v>2.331664745724993e-07</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0001639489200897515</v>
+        <v>7.564312909380533e-07</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0003844813909381628</v>
+        <v>6.058307917555794e-07</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0006660776562057436</v>
+        <v>7.54723146201286e-07</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001152395270764828</v>
+        <v>1.340144535788568e-06</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.558276512194425e-05</v>
+        <v>1.774725319592108e-06</v>
       </c>
       <c r="BI10" t="n">
-        <v>7.388061203528196e-05</v>
+        <v>7.25969016457384e-07</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001155084581114352</v>
+        <v>2.547779558881302e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0004017016326542944</v>
+        <v>2.129043195964186e-06</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0007957101333886385</v>
+        <v>2.037683941580326e-07</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0009931901004165411</v>
+        <v>1.819895942389849e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0006572005804628134</v>
+        <v>1.10595658497914e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0006583231734111905</v>
+        <v>2.147854957001982e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.482327181496657e-05</v>
+        <v>1.593094566487707e-06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.160154149867594e-05</v>
+        <v>1.184322172775865e-06</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0003305901191197336</v>
+        <v>1.375519786961377e-08</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0003528743400238454</v>
+        <v>3.222977738914778e-06</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.001119044958613813</v>
+        <v>2.536819749821007e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0001066116819856688</v>
+        <v>1.509058620285941e-07</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.000352422270225361</v>
+        <v>1.616782242308545e-06</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.617086521349847e-05</v>
+        <v>1.319771172347828e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0006321259425021708</v>
+        <v>5.330253770807758e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.002074501942843199</v>
+        <v>6.324532023427309e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.000126403640024364</v>
+        <v>3.290407676104223e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0002332446456421167</v>
+        <v>6.965048555684916e-07</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0005382315721362829</v>
+        <v>3.359793481649831e-06</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.000130061074742116</v>
+        <v>2.091293708872399e-06</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0002621499297674745</v>
+        <v>4.574511933697067e-07</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0003403945884201676</v>
+        <v>8.779397830949165e-07</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001142425098805688</v>
+        <v>7.542839739471674e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>6.026046685292386e-05</v>
+        <v>1.816214307837072e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>4.72491628897842e-05</v>
+        <v>8.334577614732552e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0001536923955427483</v>
+        <v>5.958595465926919e-07</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.000135975205921568</v>
+        <v>3.683072122839803e-07</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0003028736100532115</v>
+        <v>1.532591511477222e-07</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0003394267114344984</v>
+        <v>5.02126169976691e-07</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0002727740502450615</v>
+        <v>2.328960988506878e-07</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0009096130961552262</v>
+        <v>9.527204269943468e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0001017593458527699</v>
+        <v>1.549682565382682e-06</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0006705343257635832</v>
+        <v>5.138084816280752e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0003369178157299757</v>
+        <v>3.901930085703498e-06</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0009865046013146639</v>
+        <v>1.664139290369349e-06</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0004611184122040868</v>
+        <v>8.884651379048591e-07</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0006542251794598997</v>
+        <v>1.895939760743204e-07</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.001160290790721774</v>
+        <v>3.577132474674727e-07</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.000212791099329479</v>
+        <v>4.893627192359418e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.000369041837984696</v>
+        <v>6.007505248817324e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>7.911089778644964e-05</v>
+        <v>8.360108267879696e-07</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0001867245882749557</v>
+        <v>2.656942797329975e-06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.684381277300417e-05</v>
+        <v>1.217521457874682e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0002216842258349061</v>
+        <v>8.43822590468335e-07</v>
       </c>
       <c r="DB10" t="n">
-        <v>3.182118598488159e-05</v>
+        <v>4.024875295272068e-07</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0003230594738852233</v>
+        <v>2.968408807646483e-07</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0003193129668943584</v>
+        <v>8.63386503624497e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0001991498429561034</v>
+        <v>1.094982053473359e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0008265528595075011</v>
+        <v>7.510516297770664e-07</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001136866863816977</v>
+        <v>1.648868192205555e-06</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.001300113857723773</v>
+        <v>1.594481659594749e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0005978362751193345</v>
+        <v>1.748139311530394e-06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0006876913248561323</v>
+        <v>1.659949248278281e-06</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0005947009776718915</v>
+        <v>2.22984749598254e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0002436382492305711</v>
+        <v>3.94693097405252e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0005945373559370637</v>
+        <v>2.851702447514981e-06</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0002870197058655322</v>
+        <v>9.400188218933181e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.734959707595408e-06</v>
+        <v>2.237497653823084e-08</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0005273386486805975</v>
+        <v>1.552234891732951e-07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0003220807993784547</v>
+        <v>1.186452323054255e-06</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0008778023766353726</v>
+        <v>1.17154252166074e-06</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.001355849206447601</v>
+        <v>1.506384592175891e-06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0001372839760733768</v>
+        <v>2.466971693593223e-07</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0006639140192419291</v>
+        <v>3.322607426525792e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0001845513470470905</v>
+        <v>1.434096247976413e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0008792860899120569</v>
+        <v>1.988162807720073e-07</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0009300076635554433</v>
+        <v>1.140470885729883e-06</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.000148683087900281</v>
+        <v>1.132912302637124e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0009921748423948884</v>
+        <v>1.431710643373663e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001495207659900188</v>
+        <v>2.178637259930838e-06</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0005032281624153256</v>
+        <v>1.369714709653636e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0003570350527297705</v>
+        <v>3.502094386931276e-06</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0006486513884738088</v>
+        <v>5.657739166053943e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0002732165739871562</v>
+        <v>9.663446007834864e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.052970325574279e-06</v>
+        <v>1.628199925107765e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0003548368986230344</v>
+        <v>1.665725903876591e-07</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0002500129048712552</v>
+        <v>9.786377574982907e-08</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0003036381094716489</v>
+        <v>1.507791012045345e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.000179622758878395</v>
+        <v>1.002216436063463e-06</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.000403973157517612</v>
+        <v>1.079149910765409e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0002139910066034645</v>
+        <v>6.835537647020828e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.000182907737325877</v>
+        <v>2.816916264691827e-07</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0002514152438379824</v>
+        <v>1.437897026335122e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0004822784103453159</v>
+        <v>2.897485273933853e-08</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0007459872867912054</v>
+        <v>4.115524632197776e-07</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0008344994857907295</v>
+        <v>6.322676426862017e-07</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0002223371993750334</v>
+        <v>2.377338432779652e-06</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.000171822786796838</v>
+        <v>2.100208348565502e-06</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001186384586617351</v>
+        <v>8.045747676987958e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0005343411467038095</v>
+        <v>2.203514441134757e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0004154184716753662</v>
+        <v>3.056749164898065e-07</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0002552272635512054</v>
+        <v>1.081539267033804e-06</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0003149948315694928</v>
+        <v>4.247341394147952e-07</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0003957849112339318</v>
+        <v>1.025791107167606e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.000120718359539751</v>
+        <v>6.379636943165679e-07</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.000260612228885293</v>
+        <v>2.502902361811721e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001279430871363729</v>
+        <v>9.959276212612167e-07</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0001438080507796258</v>
+        <v>5.692539843948907e-07</v>
       </c>
       <c r="FD10" t="n">
-        <v>9.061487071448937e-05</v>
+        <v>2.626667310323683e-07</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001428480609320104</v>
+        <v>4.302196430217009e-07</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0005349211860448122</v>
+        <v>6.651894750575593e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0001465440145693719</v>
+        <v>1.080099991668249e-06</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0007123590912669897</v>
+        <v>6.494892090813664e-08</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0002874548663385212</v>
+        <v>6.028901111676532e-07</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0004135387425776571</v>
+        <v>2.356091499677859e-08</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0001298801798839122</v>
+        <v>2.2146136302581e-07</v>
       </c>
       <c r="FL10" t="n">
-        <v>5.841001257067546e-05</v>
+        <v>2.889870302169584e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0001022257420117967</v>
+        <v>5.717188855669519e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>4.11301152780652e-06</v>
+        <v>2.109374008796294e-06</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0001523666142020375</v>
+        <v>1.930618509504711e-07</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001076655928045511</v>
+        <v>1.082384983419615e-06</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0005339612253010273</v>
+        <v>3.281986209913157e-06</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0007085545221343637</v>
+        <v>9.682664767751703e-07</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0006153747672215104</v>
+        <v>1.905114004330244e-06</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0002333420561626554</v>
+        <v>9.686701787359198e-07</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0003122132620774209</v>
+        <v>2.319141231055255e-06</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.002196541056036949</v>
+        <v>8.527796921953268e-07</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.001611134270206094</v>
+        <v>7.169909395088325e-07</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0006992680137045681</v>
+        <v>5.453410722111585e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001380948000587523</v>
+        <v>4.938806341669988e-07</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001354713458567858</v>
+        <v>4.932732053930522e-07</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.001161352614872158</v>
+        <v>2.148390649381327e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002593572135083377</v>
+        <v>1.073076987267996e-06</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0008683850755915046</v>
+        <v>2.287819370394573e-06</v>
       </c>
       <c r="GD10" t="n">
-        <v>1.041650102706626e-05</v>
+        <v>1.24563257486443e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>8.183245518011972e-05</v>
+        <v>4.289127446099883e-06</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0008410447626374662</v>
+        <v>9.316696605310426e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0002679188910406083</v>
+        <v>4.132177764404332e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5.251000766293146e-05</v>
+        <v>5.144233728060499e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>8.689486094226595e-06</v>
+        <v>8.663933840580285e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>3.648485653684475e-05</v>
+        <v>9.282362952944823e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>1.720688669593073e-05</v>
+        <v>4.726668703369796e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001383884518872947</v>
+        <v>1.189329486805946e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>5.313252404448576e-05</v>
+        <v>0.0001256445684703067</v>
       </c>
       <c r="G11" t="n">
-        <v>3.370548074599355e-05</v>
+        <v>5.318421972333454e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>4.498083580983803e-05</v>
+        <v>7.289652421604842e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>6.545505311805755e-05</v>
+        <v>1.530821100459434e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.608852289791685e-05</v>
+        <v>4.45659679826349e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>6.394722004188225e-05</v>
+        <v>0.0001120066008297727</v>
       </c>
       <c r="L11" t="n">
-        <v>8.359630010090768e-05</v>
+        <v>2.91041887976462e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>1.846548002504278e-05</v>
+        <v>5.661186150973663e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>9.653798042563722e-05</v>
+        <v>6.079177182982676e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>5.915613655815832e-06</v>
+        <v>0.0001451945136068389</v>
       </c>
       <c r="P11" t="n">
-        <v>6.148599641164765e-05</v>
+        <v>2.829737422871403e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.417091622599401e-05</v>
+        <v>4.110674854018725e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.279720683873165e-05</v>
+        <v>4.034363519167528e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>2.813548417179845e-05</v>
+        <v>2.584165849839337e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>4.084645843249746e-05</v>
+        <v>2.300271262356546e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>2.158365532523021e-06</v>
+        <v>2.79443665931467e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>2.361620136070997e-05</v>
+        <v>1.714702648314415e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001024064113153145</v>
+        <v>2.491840496077202e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.848460306064226e-05</v>
+        <v>3.098916567978449e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.453309934935533e-05</v>
+        <v>1.493223680881783e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.917074329569004e-05</v>
+        <v>2.614635559439193e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.369465775904246e-05</v>
+        <v>8.656414138386026e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.848823012551293e-05</v>
+        <v>1.541315214126371e-05</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.105757736600935e-05</v>
+        <v>2.886539732571691e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>7.118072971934453e-05</v>
+        <v>1.18488424050156e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.780869934009388e-05</v>
+        <v>8.495135261910036e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.10383862699382e-05</v>
+        <v>3.070737875532359e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.31447278970154e-06</v>
+        <v>7.631255721207708e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>9.615073940949515e-05</v>
+        <v>3.582737917895429e-05</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.477389251813293e-05</v>
+        <v>0.0001050605351338163</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0001010592968668789</v>
+        <v>1.577749208081514e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.520124654547544e-06</v>
+        <v>2.706069972191472e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.811562394024804e-05</v>
+        <v>3.059366281377152e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.571282609802438e-06</v>
+        <v>7.712003025517333e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.32532246527262e-05</v>
+        <v>1.095472271117615e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.930146966828033e-05</v>
+        <v>3.497238139971159e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.927326411532704e-05</v>
+        <v>1.535785486339591e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.061664028791711e-05</v>
+        <v>1.97793597180862e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.066639667144045e-05</v>
+        <v>3.607388862292282e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.221843467646977e-05</v>
+        <v>1.504416104580741e-06</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.750706309801899e-05</v>
+        <v>9.348367711936589e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.537634125270415e-05</v>
+        <v>0.0001266896724700928</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.433109880774282e-06</v>
+        <v>3.829002889688127e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.699179695919156e-05</v>
+        <v>1.479085767641664e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0001552279718453065</v>
+        <v>5.099543705000542e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.733538662549108e-05</v>
+        <v>0.0001191557093989104</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0001232783833984286</v>
+        <v>3.546325751813129e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0001424084912287071</v>
+        <v>1.629335929465014e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.950344631040934e-05</v>
+        <v>1.741490814310964e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.51274611603003e-05</v>
+        <v>4.128644286538474e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.078482728189556e-05</v>
+        <v>5.236812285147607e-06</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.010215343441814e-05</v>
+        <v>3.821665814029984e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.178812064812519e-05</v>
+        <v>3.323330020066351e-05</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.802243322250433e-06</v>
+        <v>2.176263660658151e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.15350659750402e-05</v>
+        <v>1.156813959823921e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>9.744981798576191e-05</v>
+        <v>4.915963290841319e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3.350541737745516e-05</v>
+        <v>9.285690612159669e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.898484879347961e-05</v>
+        <v>1.330653140030336e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.058254929375835e-05</v>
+        <v>1.86414472409524e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.558534783427604e-05</v>
+        <v>3.368029865669087e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.859023127006367e-05</v>
+        <v>9.559262252878398e-07</v>
       </c>
       <c r="BO11" t="n">
-        <v>9.451970981899649e-05</v>
+        <v>1.757420795911457e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.618804839788936e-05</v>
+        <v>2.03729414351983e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.880327469436452e-05</v>
+        <v>5.37606501893606e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>8.215960406232625e-06</v>
+        <v>9.981261428038124e-06</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.742692908621393e-05</v>
+        <v>1.225819323735777e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.228630758821964e-05</v>
+        <v>4.154930866206996e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.147822280880064e-05</v>
+        <v>2.143663732567802e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.186627383111045e-06</v>
+        <v>7.107578130671754e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.442235876922496e-05</v>
+        <v>4.232906576362438e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>2.304323970747646e-05</v>
+        <v>7.099258073139936e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.31346449861303e-05</v>
+        <v>1.466047615394928e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.256000152556226e-05</v>
+        <v>4.6185014070943e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.499765782384202e-05</v>
+        <v>1.092399816116085e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>6.269300502026454e-05</v>
+        <v>1.334313310508151e-06</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.764566983794793e-05</v>
+        <v>9.313827831647359e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.0075740647153e-05</v>
+        <v>7.210846888483502e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.967120988410898e-05</v>
+        <v>3.444452158873901e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.0911760404706e-06</v>
+        <v>6.958140147617087e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.546873995219357e-05</v>
+        <v>1.548681029817089e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>2.547441545175388e-05</v>
+        <v>5.514993972610682e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>6.951871000637766e-06</v>
+        <v>2.876405415008776e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>5.37363848707173e-06</v>
+        <v>5.54175039724214e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.556926690682303e-05</v>
+        <v>3.641407602117397e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.036160140050924e-06</v>
+        <v>5.500979114003712e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.787310429790523e-05</v>
+        <v>4.258035914972425e-07</v>
       </c>
       <c r="CN11" t="n">
-        <v>4.7668581828475e-05</v>
+        <v>5.327967664925382e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>8.776662070886232e-06</v>
+        <v>2.276309351145755e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>6.640046194661409e-06</v>
+        <v>4.401216210681014e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.415335438854527e-05</v>
+        <v>1.461761530663352e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>2.045204018941149e-05</v>
+        <v>3.155641024932265e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.098219010804314e-05</v>
+        <v>3.623811790021136e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.524709452700336e-05</v>
+        <v>2.307201975781936e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.000100619756267406</v>
+        <v>4.03858666686574e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.149199852079619e-05</v>
+        <v>3.253494469390716e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.232397855550516e-05</v>
+        <v>2.375256008235738e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>7.922410077298991e-06</v>
+        <v>1.549040916870581e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>3.533123162924312e-05</v>
+        <v>7.63745356380241e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.489907481300179e-05</v>
+        <v>5.436189894680865e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.262960151711013e-05</v>
+        <v>3.260449375375174e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.702668123471085e-05</v>
+        <v>4.129924036533339e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>4.432176865520887e-06</v>
+        <v>3.733824769369676e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>9.789800060389098e-06</v>
+        <v>9.427641998627223e-06</v>
       </c>
       <c r="DE11" t="n">
-        <v>9.024627797771245e-05</v>
+        <v>2.075796328426804e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>9.20672609936446e-05</v>
+        <v>1.451936168450629e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.507330575303058e-06</v>
+        <v>1.13567803055048e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>1.148935552919284e-05</v>
+        <v>1.178798811451998e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>1.472455733164679e-05</v>
+        <v>1.61796560860239e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0001506408152636141</v>
+        <v>5.597573544946499e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>1.690850695013069e-05</v>
+        <v>8.865099516697228e-07</v>
       </c>
       <c r="DL11" t="n">
-        <v>3.290806489530951e-06</v>
+        <v>6.021045919624157e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0001047433543135412</v>
+        <v>3.270875095040537e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>2.535360181354918e-06</v>
+        <v>8.79691378941061e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.896902853739448e-05</v>
+        <v>2.800425136229023e-08</v>
       </c>
       <c r="DP11" t="n">
-        <v>3.90785098716151e-05</v>
+        <v>1.665347372181714e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5.271109330351464e-05</v>
+        <v>4.613347846316174e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.672446422977373e-05</v>
+        <v>3.274362461525016e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>1.129470365412999e-05</v>
+        <v>2.100118308590027e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>4.642163912649266e-05</v>
+        <v>2.095408490276895e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>2.166143895010464e-05</v>
+        <v>1.158852410299005e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>9.349828906124458e-05</v>
+        <v>3.955592546844855e-07</v>
       </c>
       <c r="DW11" t="n">
-        <v>2.589974792499561e-05</v>
+        <v>1.930413054651581e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>2.963001315947622e-05</v>
+        <v>1.515965414000675e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>3.119878601864912e-05</v>
+        <v>4.062616426381283e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>7.665594603167847e-05</v>
+        <v>1.979790613404475e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>5.35084618604742e-05</v>
+        <v>4.842271300731227e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>3.913194086635485e-05</v>
+        <v>1.471868472435744e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>7.029939297353849e-08</v>
+        <v>1.664511728449725e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>3.019559517269954e-05</v>
+        <v>4.72858919238206e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>2.169676736230031e-05</v>
+        <v>5.442578549263999e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>1.968694596143905e-05</v>
+        <v>3.431029654166196e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>1.30204830384173e-06</v>
+        <v>4.025011548947077e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>1.64817038239562e-07</v>
+        <v>2.76075406873133e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>7.500949141103774e-05</v>
+        <v>2.385801417403854e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>3.204861786798574e-05</v>
+        <v>2.969562592625152e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>5.210797462495975e-05</v>
+        <v>8.922548659029417e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>1.957029053301085e-05</v>
+        <v>9.919344847730827e-07</v>
       </c>
       <c r="EM11" t="n">
-        <v>3.549076791387051e-05</v>
+        <v>1.232719660038128e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>6.035852493369021e-06</v>
+        <v>1.176443038275465e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>1.336848254140932e-05</v>
+        <v>7.48167894926155e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>4.054915734741371e-06</v>
+        <v>3.017589187948033e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>5.357215286494466e-06</v>
+        <v>5.352180323825451e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>5.114432497066446e-06</v>
+        <v>1.24071266327519e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>2.174996916437522e-05</v>
+        <v>3.601967182476074e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>1.539865297672804e-05</v>
+        <v>3.670232035801746e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>2.986601612064987e-05</v>
+        <v>7.115425432857592e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>3.09511597151868e-05</v>
+        <v>3.665160329546779e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>6.417595432139933e-05</v>
+        <v>2.161607517336961e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>1.712486300675664e-05</v>
+        <v>5.471271379065001e-06</v>
       </c>
       <c r="EY11" t="n">
-        <v>1.374696785205742e-05</v>
+        <v>3.060533708776347e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>2.413916718069231e-06</v>
+        <v>3.03412366520206e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>3.571997513063252e-05</v>
+        <v>8.423163308179937e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>2.141833465429954e-05</v>
+        <v>6.175594535307027e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>3.724396947291098e-06</v>
+        <v>2.366289299970958e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>5.975362000754103e-07</v>
+        <v>6.433486760215601e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.410754677839577e-05</v>
+        <v>8.182813871826511e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>2.044439315795898e-05</v>
+        <v>3.04909008264076e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>4.957339842803776e-05</v>
+        <v>6.950566785235424e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>3.680197187350132e-05</v>
+        <v>1.631828308745753e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>2.06263066502288e-05</v>
+        <v>9.385636076331139e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>8.201898890547454e-05</v>
+        <v>3.822035068878904e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>2.474049870215822e-05</v>
+        <v>2.547587064327672e-05</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.227807115355972e-05</v>
+        <v>3.799699334194884e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.036058504018001e-05</v>
+        <v>4.930397153657395e-06</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.312142012466211e-05</v>
+        <v>2.262883936055005e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>3.482408283161931e-05</v>
+        <v>7.928800914669409e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>4.48087157565169e-05</v>
+        <v>2.96727848763112e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>1.821362093323842e-05</v>
+        <v>5.625708581646904e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>3.16072191708372e-06</v>
+        <v>1.514671021141112e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>8.460197932436131e-06</v>
+        <v>2.549069540691562e-05</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0002816588967107236</v>
+        <v>8.775026071816683e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0001006663733278401</v>
+        <v>2.787678204185795e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.923452120739967e-05</v>
+        <v>4.614889621734619e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.428872489370406e-05</v>
+        <v>0.0001312126260017976</v>
       </c>
       <c r="FX11" t="n">
-        <v>3.327739250380546e-05</v>
+        <v>1.125610651797615e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>4.956532939104363e-05</v>
+        <v>3.322500197100453e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.482255720475223e-05</v>
+        <v>1.680069181020372e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>4.46922640549019e-05</v>
+        <v>4.03244121116586e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>5.065038567408919e-05</v>
+        <v>9.766819857759401e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>5.833803879795596e-05</v>
+        <v>4.563232869259082e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>3.321362964925356e-05</v>
+        <v>5.463311390485615e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0001178183447336778</v>
+        <v>2.113672599080019e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001186910303658806</v>
+        <v>1.513393908680882e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0001276642578886822</v>
+        <v>2.613916512927972e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.000138850708026439</v>
+        <v>0.0004185877332929522</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01334600429981947</v>
+        <v>0.01081374753266573</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0005051125772297382</v>
+        <v>0.002450900617986917</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01262422651052475</v>
+        <v>0.007092859130352736</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009304528124630451</v>
+        <v>0.001202377141453326</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008043248206377029</v>
+        <v>0.006157309282571077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003055476117879152</v>
+        <v>0.00221166480332613</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003959353198297322</v>
+        <v>0.00277895200997591</v>
       </c>
       <c r="I12" t="n">
-        <v>0.005105647724121809</v>
+        <v>0.001067340490408242</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000186738179763779</v>
+        <v>0.00118263391777873</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01122438348829746</v>
+        <v>0.01032596081495285</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0006511492538265884</v>
+        <v>0.004430167842656374</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01034509763121605</v>
+        <v>0.009492380544543266</v>
       </c>
       <c r="N12" t="n">
-        <v>0.007850856520235538</v>
+        <v>0.0001245129096787423</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0059206523001194</v>
+        <v>0.006212601438164711</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003994994796812534</v>
+        <v>0.002597696147859097</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.004386312328279018</v>
+        <v>0.002276282524690032</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005015528295189142</v>
+        <v>0.0008396958583034575</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001508777786511928</v>
+        <v>0.0001876998576335609</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001130418851971626</v>
+        <v>8.680130122229457e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0003239033976569772</v>
+        <v>0.000387756124837324</v>
       </c>
       <c r="V12" t="n">
-        <v>0.003063815180212259</v>
+        <v>0.0001022166397888213</v>
       </c>
       <c r="W12" t="n">
-        <v>0.00790753960609436</v>
+        <v>0.0008385151159018278</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001100778579711914</v>
+        <v>0.001676155836321414</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.002683989005163312</v>
+        <v>9.866768959909678e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0005838593351654708</v>
+        <v>0.001631453284062445</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0005214780103415251</v>
+        <v>0.001163081033155322</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0004320290172472596</v>
+        <v>0.0004141769313719124</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0001374170533381402</v>
+        <v>0.0004952542367391288</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.00130306207574904</v>
+        <v>0.001735536963678896</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.004117508418858051</v>
+        <v>0.0006242255913093686</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.005117260850965977</v>
+        <v>0.00141868251375854</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003114842344075441</v>
+        <v>0.003482699627056718</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.001587512902915478</v>
+        <v>0.0006949516828171909</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.220527337864041e-05</v>
+        <v>0.001040288945659995</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001206375192850828</v>
+        <v>0.000700376636814326</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0005277625168673694</v>
+        <v>0.0002633058174978942</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0007161704706959426</v>
+        <v>0.002928248140960932</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0006151539855636656</v>
+        <v>0.00264501222409308</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.00061512750107795</v>
+        <v>0.002139564137905836</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.002869952935725451</v>
+        <v>0.001235409406945109</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.003019586205482483</v>
+        <v>0.002009942661970854</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.002839335706084967</v>
+        <v>0.001073305611498654</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001023430842906237</v>
+        <v>0.0003925750497728586</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0005095854867249727</v>
+        <v>0.0003083850024268031</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.105133358389139e-05</v>
+        <v>0.0003467161441221833</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.003875616006553173</v>
+        <v>0.004036263562738895</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.002561109140515327</v>
+        <v>0.002423180267214775</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.007223770953714848</v>
+        <v>0.00347768678329885</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.008315486833453178</v>
+        <v>0.004500186070799828</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.002658150624483824</v>
+        <v>0.00406490545719862</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.008738459087908268</v>
+        <v>0.0002132701774826273</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.009810945950448513</v>
+        <v>0.0003376029198989272</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0005986469914205372</v>
+        <v>0.001652215141803026</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.001375154359266162</v>
+        <v>0.0007560027297586203</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.003528874833136797</v>
+        <v>0.00131073035299778</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0006245883414521813</v>
+        <v>0.001552128233015537</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0007222288986667991</v>
+        <v>0.0003089350648224354</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.001058868831023574</v>
+        <v>0.001794123323634267</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.001883030636236072</v>
+        <v>0.0008981942082755268</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.004839041270315647</v>
+        <v>0.001324568409472704</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.002122285543009639</v>
+        <v>0.00155652582179755</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.006051639560610056</v>
+        <v>0.0009250330040231347</v>
       </c>
       <c r="BL12" t="n">
-        <v>8.761408389545977e-05</v>
+        <v>0.0001924591342685744</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0009851224021986127</v>
+        <v>0.001007442711852491</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.001536747557111084</v>
+        <v>8.937850361689925e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.005374450236558914</v>
+        <v>0.0009595447336323559</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.002588144270703197</v>
+        <v>0.0001870093256002292</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0007165262359194458</v>
+        <v>0.0008426086278632283</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.001717878738418221</v>
+        <v>3.682747774291784e-05</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.004281484521925449</v>
+        <v>0.001100041903555393</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.002837501233443618</v>
+        <v>0.0008726612431928515</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.001759465783834457</v>
+        <v>2.579996362328529e-06</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.005348433740437031</v>
+        <v>0.003608300816267729</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0003078992594964802</v>
+        <v>0.001644028583541512</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.008391357958316803</v>
+        <v>0.003584985854104161</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.007409264333546162</v>
+        <v>0.0009459408465772867</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0005321436328813434</v>
+        <v>0.002383555518463254</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.004293672740459442</v>
+        <v>0.0003220716607756913</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.003141295863315463</v>
+        <v>0.0006180088967084885</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.001436273683793843</v>
+        <v>6.96847855579108e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.926815356360748e-05</v>
+        <v>0.0003278705407865345</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.00143137073609978</v>
+        <v>0.003315693000331521</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001943648385349661</v>
+        <v>0.0005290333065204322</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.001835820381529629</v>
+        <v>0.00263200094923377</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0008959927945397794</v>
+        <v>0.000486736127641052</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0006007826304994524</v>
+        <v>0.001049027894623578</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.00105400918982923</v>
+        <v>4.794686537934467e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0002978375996463001</v>
+        <v>0.0002161255106329918</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0009938585571944714</v>
+        <v>0.0006615598103962839</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0002516773238312453</v>
+        <v>0.0004732888482976705</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.003127865958958864</v>
+        <v>0.0004847237723879516</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0007665205048397183</v>
+        <v>0.004080807790160179</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.001521399128250778</v>
+        <v>0.00418535154312849</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.00114411860704422</v>
+        <v>0.0008137782569974661</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.003372999140992761</v>
+        <v>0.000390322005841881</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.003133660182356834</v>
+        <v>0.0002369244175497442</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.004668138455599546</v>
+        <v>0.001645635114982724</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0007432398269884288</v>
+        <v>0.0001318538270425051</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.282825542148203e-05</v>
+        <v>0.0003014523535966873</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.00204925169236958</v>
+        <v>0.003190739545971155</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0004327805363573134</v>
+        <v>0.0008691616822034121</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.001668130746111274</v>
+        <v>0.002540609566494823</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001890324056148529</v>
+        <v>0.0003857951378449798</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0008342678193002939</v>
+        <v>0.001220925827510655</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0007404271746054292</v>
+        <v>6.755829963367432e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0004625493020284921</v>
+        <v>0.0005821232334710658</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001047867117449641</v>
+        <v>0.0002332677540834993</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0006797765381634235</v>
+        <v>0.001391040626913309</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.005597962532192469</v>
+        <v>0.001708308467641473</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0003837732365354896</v>
+        <v>0.00135246675927192</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.007205008529126644</v>
+        <v>0.002467538695782423</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0060142632573843</v>
+        <v>0.0007482661749236286</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.003080856753513217</v>
+        <v>0.007595418486744165</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.003204186446964741</v>
+        <v>4.287263436708599e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.00128857628442347</v>
+        <v>0.004188788589090109</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.002624302404001355</v>
+        <v>0.003111230675131083</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.002437630202621222</v>
+        <v>0.0007882944773882627</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.003923848271369934</v>
+        <v>0.002148909959942102</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.001306304126046598</v>
+        <v>1.894653541967273e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.004745263606309891</v>
+        <v>0.001059297355823219</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0002072083007078618</v>
+        <v>0.000597038131672889</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.001029086532071233</v>
+        <v>0.0003124797658529133</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.001196167897433043</v>
+        <v>0.000201210510567762</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.001390268327668309</v>
+        <v>0.001351811690256</v>
       </c>
       <c r="DV12" t="n">
-        <v>8.822798554319888e-05</v>
+        <v>0.003195679048076272</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.001266636420041323</v>
+        <v>1.365214120596647e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0003268042637500912</v>
+        <v>0.0002025262219831347</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001731378259137273</v>
+        <v>0.002087944420054555</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.002619674196466804</v>
+        <v>0.002372608985751867</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.003981403540819883</v>
+        <v>0.0003069585072807968</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0005368028068915009</v>
+        <v>0.002472365973517299</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0006240768125280738</v>
+        <v>0.0005074837827123702</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.002001312095671892</v>
+        <v>0.004183970391750336</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0005123240407556295</v>
+        <v>0.004234842956066132</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0007237490499392152</v>
+        <v>0.001814560848288238</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0003189790295436978</v>
+        <v>0.002285846043378115</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.001182259176857769</v>
+        <v>0.001457781996577978</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0001321472809650004</v>
+        <v>0.002648493507876992</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.002256616950035095</v>
+        <v>0.0007740631699562073</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0006941435276530683</v>
+        <v>0.0004606230359058827</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.001135686645284295</v>
+        <v>0.0002164279139833525</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0003657171619124711</v>
+        <v>0.000229204713832587</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0002366129192523658</v>
+        <v>0.0003533554263412952</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0008923212299123406</v>
+        <v>0.0008825326804071665</v>
       </c>
       <c r="EP12" t="n">
-        <v>6.393952207872644e-05</v>
+        <v>0.003357089590281248</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0002086526656057686</v>
+        <v>0.0006604516529478133</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.003419179003685713</v>
+        <v>0.001152081415057182</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.001194667303934693</v>
+        <v>0.0002762615331448615</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.007419535890221596</v>
+        <v>2.504093572497368e-07</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.003890689229592681</v>
+        <v>0.001175551908090711</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.001070488360710442</v>
+        <v>0.001432090648449957</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.004848964512348175</v>
+        <v>0.001685468829236925</v>
       </c>
       <c r="EX12" t="n">
-        <v>6.320963439065963e-05</v>
+        <v>0.0002307078684680164</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.001305481302551925</v>
+        <v>0.00327131524682045</v>
       </c>
       <c r="EZ12" t="n">
-        <v>8.133619849104434e-05</v>
+        <v>0.0006837213295511901</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.002390220062807202</v>
+        <v>0.003036842681467533</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0006571959238499403</v>
+        <v>0.0004670080379582942</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0008567907498218119</v>
+        <v>0.001054620137438178</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.001891713589429855</v>
+        <v>0.0001477475598221645</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0008822148665785789</v>
+        <v>0.0005994303501211107</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001342070288956165</v>
+        <v>6.285174458753318e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0003747490991372615</v>
+        <v>0.000722126686014235</v>
       </c>
       <c r="FH12" t="n">
-        <v>8.551873179385439e-05</v>
+        <v>0.001015650341287255</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.002437958028167486</v>
+        <v>5.622650496661663e-05</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001545121660456061</v>
+        <v>0.0007269580382853746</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.004051214549690485</v>
+        <v>0.002065425040200353</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.003817651886492968</v>
+        <v>0.000217632157728076</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0009143347851932049</v>
+        <v>0.0001023386721499264</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.00165887305047363</v>
+        <v>0.001262128120288253</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.001677484251558781</v>
+        <v>0.001905627548694611</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.001204223488457501</v>
+        <v>0.001209949143230915</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.003532396629452705</v>
+        <v>0.004368885420262814</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.001133281271904707</v>
+        <v>0.001854500849731266</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.003846524748951197</v>
+        <v>0.001934877713210881</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.009801417589187622</v>
+        <v>0.006836550775915384</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.004126905929297209</v>
+        <v>0.001967089250683784</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.003069516271352768</v>
+        <v>0.0005397824570536613</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.002243167487904429</v>
+        <v>0.002148848026990891</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0009377174428664148</v>
+        <v>0.003168913535773754</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0004552550090011209</v>
+        <v>0.001066177152097225</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0008928063907660544</v>
+        <v>0.0002670107642188668</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0008397130877710879</v>
+        <v>0.001418693223968148</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.001854491303674877</v>
+        <v>0.002047702437266707</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.003826095955446362</v>
+        <v>8.02140129962936e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.001112200669012964</v>
+        <v>0.001828368054702878</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0007209465838968754</v>
+        <v>0.00227442430332303</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.002565388334915042</v>
+        <v>0.0002889488532673568</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.003099927678704262</v>
+        <v>0.0009584236540831625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0002791601582430303</v>
+        <v>0.001779250684194267</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001668465789407492</v>
+        <v>0.003364463336765766</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002775951288640499</v>
+        <v>0.001541309640742838</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001593884429894388</v>
+        <v>0.003251987975090742</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0004925940884277225</v>
+        <v>0.0002884985879063606</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001215839991346002</v>
+        <v>0.01019864249974489</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005909869214519858</v>
+        <v>0.00469418428838253</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008052054909057915</v>
+        <v>0.004241460002958775</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006475569680333138</v>
+        <v>0.001767162466421723</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002828036085702479</v>
+        <v>0.001579612726345658</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001553048845380545</v>
+        <v>0.005566076841205359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0002852293837349862</v>
+        <v>0.0007490115822292864</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001276931376196444</v>
+        <v>0.002928226953372359</v>
       </c>
       <c r="N13" t="n">
-        <v>7.235459634102881e-06</v>
+        <v>0.001519373967312276</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001002581790089607</v>
+        <v>0.01004835218191147</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0007934205932542682</v>
+        <v>0.006649167742580175</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0007171686156652868</v>
+        <v>0.004564212169498205</v>
       </c>
       <c r="R13" t="n">
-        <v>8.265374344773591e-05</v>
+        <v>0.0002564409514889121</v>
       </c>
       <c r="S13" t="n">
-        <v>8.488347521051764e-05</v>
+        <v>0.001060221344232559</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002872671175282449</v>
+        <v>0.001740260166116059</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000195915752556175</v>
+        <v>0.001109858741983771</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0005568602355197072</v>
+        <v>0.002207390964031219</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00117256841622293</v>
+        <v>0.004637925419956446</v>
       </c>
       <c r="X13" t="n">
-        <v>0.000446642137831077</v>
+        <v>0.002645529340952635</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.599635187536478e-05</v>
+        <v>0.0008764674421399832</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0003617394831962883</v>
+        <v>0.0006896964041516185</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.461415225407109e-05</v>
+        <v>0.0006082592299208045</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56516907736659e-05</v>
+        <v>0.0001829750835895538</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0001072438462870196</v>
+        <v>0.002642605686560273</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.74557624431327e-05</v>
+        <v>0.003100746544077992</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0002666743821464479</v>
+        <v>0.002974064089357853</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.725468508899212e-05</v>
+        <v>0.002538153901696205</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0001257176918443292</v>
+        <v>0.002635005861520767</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0001891491992864758</v>
+        <v>0.001048975740559399</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0004080794169567525</v>
+        <v>0.002816212829202414</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0002971151552628726</v>
+        <v>0.001083875191397965</v>
       </c>
       <c r="AK13" t="n">
-        <v>7.312206435017288e-06</v>
+        <v>0.0009359732503071427</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0001826665393309668</v>
+        <v>0.001296455506235361</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.944041287060827e-05</v>
+        <v>0.0006752614863216877</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0004614354111254215</v>
+        <v>0.001915354747325182</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001263640879187733</v>
+        <v>0.0004626836744137108</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0001630011101951823</v>
+        <v>0.002624456770718098</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0001505277323303744</v>
+        <v>0.0007523783133365214</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0003656185872387141</v>
+        <v>0.001113224192522466</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.760074079968035e-05</v>
+        <v>0.002294053323566914</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0004197533125989139</v>
+        <v>0.0008814730099402368</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0003277248470112681</v>
+        <v>0.006465455051511526</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.457456326344982e-05</v>
+        <v>0.001620174618437886</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001181675703264773</v>
+        <v>0.001260362099856138</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001560989418067038</v>
+        <v>0.002710417378693819</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.000989771680906415</v>
+        <v>0.002729405416175723</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0009205908863805234</v>
+        <v>0.002762150950729847</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0007383190095424652</v>
+        <v>0.003890080843120813</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0004440735501702875</v>
+        <v>0.0009409763151779771</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.000346840126439929</v>
+        <v>0.0008010226301848888</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0006515113636851311</v>
+        <v>0.001075925189070404</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0003481538442429155</v>
+        <v>0.0008928879396989942</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0007141001988202333</v>
+        <v>0.0019287922186777</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0002240429457742721</v>
+        <v>0.001639303052797914</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0003439347783569247</v>
+        <v>0.004337246529757977</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.001018351991660893</v>
+        <v>0.001739291474223137</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0004456714086700231</v>
+        <v>0.003000370925292373</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0002962510334327817</v>
+        <v>0.002767228055745363</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.000161935604410246</v>
+        <v>0.00120920839253813</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0003246600099373609</v>
+        <v>0.0003432334924582392</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.000280369509709999</v>
+        <v>0.001273143338039517</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.00112292286939919</v>
+        <v>0.000727896869648248</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0006116802105680108</v>
+        <v>0.0003897044807672501</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0001481071230955422</v>
+        <v>0.002451657550409436</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002318446058779955</v>
+        <v>0.001297789509408176</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.001117881038226187</v>
+        <v>0.001018319744616747</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0003381493734195828</v>
+        <v>0.0001505288819316775</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.000153573535499163</v>
+        <v>0.0005946637247689068</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0003842993173748255</v>
+        <v>0.001675252104178071</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0003018113202415407</v>
+        <v>0.001796669443137944</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0004181060648988932</v>
+        <v>0.003183353692293167</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0004868910764344037</v>
+        <v>0.004123406950384378</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.000885724788531661</v>
+        <v>0.005881885532289743</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0006465625483542681</v>
+        <v>0.0006829658523201942</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0003660618385765702</v>
+        <v>0.002463223645463586</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001167583250207826</v>
+        <v>0.000619026948697865</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.41984341503121e-05</v>
+        <v>0.000750440638512373</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0002006848226301372</v>
+        <v>0.0006243151146918535</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0002113252994604409</v>
+        <v>6.855821993667632e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.974703213316388e-05</v>
+        <v>0.00137782352976501</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.000136228118208237</v>
+        <v>0.0003863933379761875</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.000109166132460814</v>
+        <v>0.002711842069402337</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.765081833582371e-06</v>
+        <v>0.0005065526347607374</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0002145127509720623</v>
+        <v>0.001829140353947878</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001185569417430088</v>
+        <v>0.0001964879920706153</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0001165506619145162</v>
+        <v>0.001512610004283488</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.000320294959237799</v>
+        <v>0.001436350983567536</v>
       </c>
       <c r="CO13" t="n">
-        <v>3.174457742716186e-05</v>
+        <v>0.0006872508674860001</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.248763121315278e-05</v>
+        <v>0.0006534264539368451</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.000948626606259495</v>
+        <v>0.006003974005579948</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0002365352265769616</v>
+        <v>0.004122612066566944</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0008577174739912152</v>
+        <v>2.559833228588104e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0005261592450551689</v>
+        <v>0.001529292552731931</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001668169716140255</v>
+        <v>0.001619117450900376</v>
       </c>
       <c r="CV13" t="n">
-        <v>4.647727837436832e-05</v>
+        <v>0.001041567884385586</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002294126752531156</v>
+        <v>0.000514055194798857</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0002289270050823689</v>
+        <v>0.0002040214312728494</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.962247188203037e-05</v>
+        <v>0.001621868927031755</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.718421637837309e-05</v>
+        <v>0.0005395828047767282</v>
       </c>
       <c r="DA13" t="n">
-        <v>6.901651795487851e-05</v>
+        <v>0.002453785622492433</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001105498449760489</v>
+        <v>0.0004984151455573738</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001532167661935091</v>
+        <v>0.001396871404722333</v>
       </c>
       <c r="DD13" t="n">
-        <v>7.753886166028678e-05</v>
+        <v>3.9651058614254e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.000911930575966835</v>
+        <v>0.0009555338183417916</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0009778919629752636</v>
+        <v>0.001410466618835926</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0001805041829356924</v>
+        <v>0.00283741788007319</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.001062787021510303</v>
+        <v>0.001968242228031158</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0002299828047398478</v>
+        <v>6.551270780619234e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.00146596331615001</v>
+        <v>0.002330110175535083</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0005571070360019803</v>
+        <v>0.001178348204120994</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0001956664491444826</v>
+        <v>0.001991230761632323</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.000599463761318475</v>
+        <v>0.0007202924462035298</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.000401644705561921</v>
+        <v>0.0003470717056188732</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0003745775320567191</v>
+        <v>2.510072226868942e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0002300685155205429</v>
+        <v>0.001212689559906721</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.000229887169552967</v>
+        <v>0.004005383234471083</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0001830128603614867</v>
+        <v>0.002672031288966537</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0004409933171700686</v>
+        <v>0.003914774395525455</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0002418793592369184</v>
+        <v>0.002978387288749218</v>
       </c>
       <c r="DU13" t="n">
-        <v>6.4014398958534e-05</v>
+        <v>0.003666711738333106</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0002648491063155234</v>
+        <v>0.0008591681253165007</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001398585009155795</v>
+        <v>0.00176509574521333</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.826791938394308e-05</v>
+        <v>0.0007304620812647045</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0001353362313238904</v>
+        <v>0.003510590875521302</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0007226521847769618</v>
+        <v>0.001123107504099607</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0001946143165696412</v>
+        <v>6.942197796888649e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0008299402543343604</v>
+        <v>0.002059563063085079</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002495822554919869</v>
+        <v>0.002212599152699113</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002353880554437637</v>
+        <v>0.001271792920306325</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007058926275931299</v>
+        <v>0.0007993386825546622</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0001398075255565345</v>
+        <v>0.001639894675463438</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0006526774377562106</v>
+        <v>0.001790737267583609</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002053327771136537</v>
+        <v>0.0004381860489957035</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.000438026268966496</v>
+        <v>0.002526358235627413</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.000271406548563391</v>
+        <v>0.000402055709855631</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0002752183354459703</v>
+        <v>0.001068384968675673</v>
       </c>
       <c r="EL13" t="n">
-        <v>8.435160998487845e-05</v>
+        <v>0.0006375424563884735</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0004218693647999316</v>
+        <v>0.002250778488814831</v>
       </c>
       <c r="EN13" t="n">
-        <v>3.127702439087443e-05</v>
+        <v>0.0004215718945488334</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0003133163263555616</v>
+        <v>0.001282299868762493</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0002488577738404274</v>
+        <v>0.0002131251967512071</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001682795555097982</v>
+        <v>0.001092886435799301</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0002745242672972381</v>
+        <v>0.001000209827907383</v>
       </c>
       <c r="ES13" t="n">
-        <v>8.029614400584251e-05</v>
+        <v>0.0007298772688955069</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0002805947442539036</v>
+        <v>0.002279569627717137</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0004567610158119351</v>
+        <v>0.003178551327437162</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0008006470743566751</v>
+        <v>0.0005573000526055694</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0001132128454628401</v>
+        <v>0.0002739739429671317</v>
       </c>
       <c r="EX13" t="n">
-        <v>3.015212678292301e-05</v>
+        <v>0.001255218521691859</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0002258861204609275</v>
+        <v>0.0006738118827342987</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001668891200097278</v>
+        <v>0.0004351360257714987</v>
       </c>
       <c r="FA13" t="n">
-        <v>3.539132012519985e-05</v>
+        <v>0.001518947770819068</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001465746900066733</v>
+        <v>0.0002968325279653072</v>
       </c>
       <c r="FC13" t="n">
-        <v>3.992200072389096e-05</v>
+        <v>0.002262706169858575</v>
       </c>
       <c r="FD13" t="n">
-        <v>8.320393681060523e-05</v>
+        <v>0.0004684311570599675</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0003421260043978691</v>
+        <v>0.001231678179465234</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001903485244838521</v>
+        <v>0.0001473307056585327</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0004626559966709465</v>
+        <v>0.003967673052102327</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0001289916108362377</v>
+        <v>0.001666208845563233</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0002092164359055459</v>
+        <v>0.001679400214925408</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0005837984499521554</v>
+        <v>0.0001747897622408345</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001270294596906751</v>
+        <v>0.001317627029493451</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0009147676173597574</v>
+        <v>0.001645236276090145</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0001093681930797175</v>
+        <v>0.0005796265322715044</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001843953359639272</v>
+        <v>0.0008653491386212409</v>
       </c>
       <c r="FO13" t="n">
-        <v>1.79081253008917e-05</v>
+        <v>0.00152208108920604</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0001136037462856621</v>
+        <v>0.002956611569970846</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0008167413761839271</v>
+        <v>0.007052818778902292</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.000386634113965556</v>
+        <v>0.002284307032823563</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0005091443890705705</v>
+        <v>0.0009992532432079315</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0020832191221416</v>
+        <v>0.007930542342364788</v>
       </c>
       <c r="FU13" t="n">
-        <v>2.331128780497238e-05</v>
+        <v>0.003157090395689011</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001062555471435189</v>
+        <v>0.004500745795667171</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0005611787782981992</v>
+        <v>0.0007701144786551595</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.000528094416949898</v>
+        <v>0.0004331901436671615</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0003466398629825562</v>
+        <v>0.0006257849163375795</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0006129287648946047</v>
+        <v>0.0008040267275646329</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0001053554951795377</v>
+        <v>0.001901376992464066</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0009706126293167472</v>
+        <v>0.001388212433084846</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0001564237172715366</v>
+        <v>0.001005476457066834</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0002045866713160649</v>
+        <v>0.002507323166355491</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.000339835649356246</v>
+        <v>0.001509603345766664</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0007490382995456457</v>
+        <v>2.425390994176269e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0005387855926528573</v>
+        <v>0.00142030359711498</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0002139683929271996</v>
+        <v>9.674493412603624e-06</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002852493897080421</v>
+        <v>0.0001590087485965341</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001725863548927009</v>
+        <v>1.412623532814905e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001335340784862638</v>
+        <v>0.0001298640563618392</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0005609900690615177</v>
+        <v>3.101245602010749e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.448604780307505e-05</v>
+        <v>0.0001110449156840332</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000235577259445563</v>
+        <v>4.773723412654363e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>8.771513967076316e-05</v>
+        <v>4.808255107491277e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0002424022386549041</v>
+        <v>7.869296496210154e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>7.837687735445797e-05</v>
+        <v>2.931313247245271e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.002147547900676727</v>
+        <v>0.0001663191942498088</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001410979893989861</v>
+        <v>3.70568668586202e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001137580606155097</v>
+        <v>0.0001842893689172342</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0007424495415762067</v>
+        <v>7.152933540055528e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0002394094044575468</v>
+        <v>0.0001186161607620306</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001383521012030542</v>
+        <v>1.281226104765665e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0004019899643026292</v>
+        <v>1.240818528458476e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.182810203521512e-05</v>
+        <v>1.602806514711119e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.276360853808001e-05</v>
+        <v>9.172607860818971e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003311237378511578</v>
+        <v>1.03379297797801e-05</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001543817779747769</v>
+        <v>1.247013278771192e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0003678711946122348</v>
+        <v>2.918079371738713e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0004538115754257888</v>
+        <v>4.409931352711283e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002357070043217391</v>
+        <v>4.134961272939108e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.515874651493505e-05</v>
+        <v>4.247325705364347e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000250467041041702</v>
+        <v>9.079031769942958e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.454428951954469e-05</v>
+        <v>2.00903887161985e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001218255056301132</v>
+        <v>2.788282017718302e-06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0002659688761923462</v>
+        <v>1.999217056436464e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001505334221292287</v>
+        <v>2.424554622848518e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0001392141712130979</v>
+        <v>3.704435584950261e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.76660124049522e-05</v>
+        <v>6.220546310942154e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0003785045119002461</v>
+        <v>5.820395381306298e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>8.085919398581609e-05</v>
+        <v>5.584618520515505e-06</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0002538106054998934</v>
+        <v>6.364450382534415e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.489644874818623e-06</v>
+        <v>2.264478280267213e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0003855658869724721</v>
+        <v>1.554666960146278e-05</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.237896013772115e-05</v>
+        <v>5.305853119352832e-05</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.349577547051013e-05</v>
+        <v>3.421260043978691e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002709577674977481</v>
+        <v>5.377339766710065e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0004159228992648423</v>
+        <v>8.959879778558388e-06</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0004568551375996321</v>
+        <v>3.071156970690936e-05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.704721610934939e-06</v>
+        <v>3.17675803671591e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0002693894784897566</v>
+        <v>3.32309650730167e-06</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.420162779046223e-05</v>
+        <v>1.265850369236432e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.783674037549645e-05</v>
+        <v>2.814430627040565e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001671495498158038</v>
+        <v>0.0001355309359496459</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.411676203133538e-05</v>
+        <v>2.351318289584015e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0004992579342797399</v>
+        <v>3.079876842093654e-05</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.158384010428563e-05</v>
+        <v>4.031676144222729e-05</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.203638359787874e-06</v>
+        <v>7.26070356904529e-05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001130640666815452</v>
+        <v>1.201563645736314e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001018966067931615</v>
+        <v>1.181511106551625e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0002404517435934395</v>
+        <v>8.884813723852858e-06</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0002472485066391528</v>
+        <v>8.92006755748298e-06</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0005175013211555779</v>
+        <v>7.599402124469634e-06</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.000487877958221361</v>
+        <v>2.885380490624812e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0002459851384628564</v>
+        <v>3.830001151072793e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0008490387117490172</v>
+        <v>1.140085259976331e-06</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0002429332234896719</v>
+        <v>2.294157638971228e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0003113580751232803</v>
+        <v>9.777555533219129e-06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0001559865922899917</v>
+        <v>7.164629641920328e-05</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.320413816254586e-05</v>
+        <v>2.111007961502764e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>9.306105494033545e-05</v>
+        <v>2.749158511505811e-06</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.000419927149778232</v>
+        <v>2.278999090776779e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0002064931468339637</v>
+        <v>3.601262051233789e-06</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.003860860597342e-05</v>
+        <v>5.256398799247108e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0004134871414862573</v>
+        <v>6.788268365198746e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.000312729476718232</v>
+        <v>1.153902030637255e-05</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001250600180355832</v>
+        <v>7.689158337598201e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.098640420124866e-05</v>
+        <v>4.235078449710272e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0001941957743838429</v>
+        <v>2.16316166188335e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0002957970718853176</v>
+        <v>2.497477908036672e-05</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0009596176678314805</v>
+        <v>9.303562546847388e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0001554449700051919</v>
+        <v>1.392799276800361e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0002109347842633724</v>
+        <v>7.334188558161259e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.564215745020192e-05</v>
+        <v>2.785871402011253e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.000365525484085083</v>
+        <v>4.170969259575941e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.113292718306184e-05</v>
+        <v>3.194686541974079e-06</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0001403550559189171</v>
+        <v>8.689576134202071e-06</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0001005598169285804</v>
+        <v>1.837459240050521e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001133883124566637</v>
+        <v>1.110619177779881e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0004839369212277234</v>
+        <v>4.573066689772531e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001291750086238608</v>
+        <v>5.895622052776162e-07</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0002099034754792228</v>
+        <v>4.422947677085176e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>8.957286627264693e-05</v>
+        <v>4.232537662574032e-07</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.778181103873067e-05</v>
+        <v>1.44386203828617e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001470480783609673</v>
+        <v>3.330727395223221e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0001014832232613117</v>
+        <v>1.547675128676929e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.77213460119674e-05</v>
+        <v>3.192399844920146e-06</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0008601742447353899</v>
+        <v>4.448007530299947e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0001408801908837631</v>
+        <v>6.342964479699731e-05</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.98798061319394e-05</v>
+        <v>5.151664663571864e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>4.747675484395586e-05</v>
+        <v>9.057969145942479e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002317730686627328</v>
+        <v>1.440329378965544e-05</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0009543364867568016</v>
+        <v>3.699838089232799e-06</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0001971022866200656</v>
+        <v>2.656085780472495e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0001924737152876332</v>
+        <v>7.117384666344151e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0004221346462145448</v>
+        <v>8.851697202771902e-06</v>
       </c>
       <c r="CV14" t="n">
-        <v>7.964962424011901e-05</v>
+        <v>3.233570623706328e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0004793805710505694</v>
+        <v>4.022100620204583e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0002447034639772028</v>
+        <v>4.78382798974053e-06</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0002675902505870908</v>
+        <v>4.641238774638623e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>6.960328755667433e-05</v>
+        <v>1.517199962108862e-05</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.781817213166505e-05</v>
+        <v>1.752331991156098e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>9.9842349300161e-05</v>
+        <v>6.967784884182038e-06</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001662200957071036</v>
+        <v>2.004692760237958e-05</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.863171019067522e-05</v>
+        <v>4.707328116637655e-06</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0003480666782706976</v>
+        <v>1.698931555438321e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0008719406323507428</v>
+        <v>1.97549943550257e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0005325279198586941</v>
+        <v>3.027742059202865e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0005121889989823103</v>
+        <v>2.830978701240383e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>5.6819299061317e-05</v>
+        <v>8.982773579191417e-06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>9.578673052601516e-05</v>
+        <v>4.871909186476842e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.000453033106168732</v>
+        <v>2.073412724712398e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0003717282088473439</v>
+        <v>0.0001093495957320556</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.000134363304823637</v>
+        <v>1.759554288582876e-05</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0002917022502515465</v>
+        <v>1.214861003973056e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001052069419529289</v>
+        <v>4.263575465301983e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>3.550519977579825e-06</v>
+        <v>5.663549927703571e-06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004348168440628797</v>
+        <v>1.827421510824934e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.096316742012277e-05</v>
+        <v>6.750681677658577e-06</v>
       </c>
       <c r="DS14" t="n">
-        <v>5.855906783835962e-05</v>
+        <v>2.868630645025405e-06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0001311222149524838</v>
+        <v>7.812708645360544e-06</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0002118213305948302</v>
+        <v>7.023954822216183e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0001893235312309116</v>
+        <v>3.67377870134078e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0002460935502313077</v>
+        <v>1.226819404109847e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.000188328413059935</v>
+        <v>1.01193472801242e-06</v>
       </c>
       <c r="DY14" t="n">
-        <v>1.125798735301942e-05</v>
+        <v>2.497785317245871e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0001559924421599135</v>
+        <v>3.315634239697829e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003479626029729843</v>
+        <v>2.082356149912812e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0003400064597371966</v>
+        <v>1.546135717944708e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.000425836507929489</v>
+        <v>2.863477311620954e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>5.825063999509439e-05</v>
+        <v>9.769514144863933e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0001968019059859216</v>
+        <v>4.931730654789135e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0004421196063049138</v>
+        <v>3.683780960272998e-06</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0004460913187358528</v>
+        <v>1.246266492671566e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.000482443138025701</v>
+        <v>2.018238592427224e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0002689263201318681</v>
+        <v>3.565726728993468e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001379294699290767</v>
+        <v>3.277404175605625e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.702617712202482e-05</v>
+        <v>1.413637528457912e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>8.738604810787365e-05</v>
+        <v>3.313954266559449e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>5.882781624677591e-05</v>
+        <v>1.231810165336356e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>7.37807567929849e-06</v>
+        <v>6.374898021022091e-06</v>
       </c>
       <c r="EO14" t="n">
-        <v>9.788740135263652e-05</v>
+        <v>6.688932444376405e-06</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0004970589652657509</v>
+        <v>4.053490556543693e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>8.656946738483384e-05</v>
+        <v>5.556766154768411e-06</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0003941062896046788</v>
+        <v>1.435409740224713e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0001642085844650865</v>
+        <v>3.117923552053981e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>7.15026690158993e-05</v>
+        <v>1.276196053368039e-05</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0002736841270234436</v>
+        <v>1.96464461623691e-05</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0001327361533185467</v>
+        <v>3.611894135246985e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>6.863546150270849e-05</v>
+        <v>4.66608144051861e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0001787970250006765</v>
+        <v>1.114238784793997e-05</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0004914595047011971</v>
+        <v>4.767522113979794e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0001741244341246784</v>
+        <v>5.852916729054414e-08</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0002635899290908128</v>
+        <v>5.620250885840505e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>5.757692997576669e-05</v>
+        <v>2.255236722703557e-06</v>
       </c>
       <c r="FC14" t="n">
-        <v>1.477759724366479e-05</v>
+        <v>2.011210744967684e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001297377166338265</v>
+        <v>5.363353920984082e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.00016187404980883</v>
+        <v>2.757842230494134e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>6.027974450262263e-05</v>
+        <v>5.702483576897066e-06</v>
       </c>
       <c r="FG14" t="n">
-        <v>1.394197170156986e-05</v>
+        <v>4.811270628124475e-06</v>
       </c>
       <c r="FH14" t="n">
-        <v>5.743243673350662e-05</v>
+        <v>1.271063410968054e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0001440389896743</v>
+        <v>8.73086628416786e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0003540755715221167</v>
+        <v>4.00350327254273e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.00028561832732521</v>
+        <v>7.275052212207811e-06</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0001890962012112141</v>
+        <v>2.783537638606504e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>5.343204611563124e-05</v>
+        <v>3.966678832512116e-06</v>
       </c>
       <c r="FN14" t="n">
-        <v>7.350218947976828e-05</v>
+        <v>1.626376615604386e-06</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0001032764339470305</v>
+        <v>3.164593363180757e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0006251265876926482</v>
+        <v>1.445080124540254e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>8.305320079671219e-05</v>
+        <v>2.952630529762246e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0008377510821446776</v>
+        <v>7.574701157864183e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>2.71683147730073e-05</v>
+        <v>2.197946378146298e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002159091818612069</v>
+        <v>5.152910307515413e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0001986950519494712</v>
+        <v>1.727860762912314e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0003858245036099106</v>
+        <v>1.317874557571486e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.000181613489985466</v>
+        <v>8.2678314356599e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0003307248698547482</v>
+        <v>3.23762674270256e-06</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0001069883655873127</v>
+        <v>1.399776192556601e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001390701218042523</v>
+        <v>1.150141724792775e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>6.941190804354846e-05</v>
+        <v>9.377473361382727e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>2.570287506387103e-05</v>
+        <v>9.767911251401529e-06</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.000127893450553529</v>
+        <v>5.164232061360963e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001054232780006714</v>
+        <v>3.924145858036354e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.000360428006388247</v>
+        <v>4.976867785444483e-05</v>
       </c>
       <c r="GF14" t="n">
-        <v>4.279726636013947e-05</v>
+        <v>1.870785854407586e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001019582632579841</v>
+        <v>2.683470484043937e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.02594318985939026</v>
+        <v>0.01013630628585815</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3475268185138702</v>
+        <v>0.7311697006225586</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1231445446610451</v>
+        <v>0.1183383762836456</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008661026135087013</v>
+        <v>0.3229098618030548</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01342079974710941</v>
+        <v>0.1633830517530441</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07997775822877884</v>
+        <v>0.1478129923343658</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01763477548956871</v>
+        <v>0.3179226517677307</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06365422904491425</v>
+        <v>0.3611291348934174</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01505524665117264</v>
+        <v>0.09113293141126633</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1088123917579651</v>
+        <v>0.1513692885637283</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3395982682704926</v>
+        <v>0.7963461875915527</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08378876000642776</v>
+        <v>0.1212896779179573</v>
       </c>
       <c r="M15" t="n">
-        <v>0.007350843399763107</v>
+        <v>0.5571187138557434</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08922919631004333</v>
+        <v>0.3710955679416656</v>
       </c>
       <c r="O15" t="n">
-        <v>0.002781086135655642</v>
+        <v>0.02061838656663895</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04508696496486664</v>
+        <v>0.3808188438415527</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09291313588619232</v>
+        <v>0.2837093472480774</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03458975255489349</v>
+        <v>0.1878241151571274</v>
       </c>
       <c r="S15" t="n">
-        <v>0.03855692595243454</v>
+        <v>0.003824992105364799</v>
       </c>
       <c r="T15" t="n">
-        <v>0.02487541921436787</v>
+        <v>0.008684850297868252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.05558227002620697</v>
+        <v>0.0289105698466301</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04974659159779549</v>
+        <v>0.07306627184152603</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01656754687428474</v>
+        <v>0.03561723604798317</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002099481411278248</v>
+        <v>0.02885418012738228</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002355905249714851</v>
+        <v>0.03992230072617531</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.02936372719705105</v>
+        <v>0.08317753672599792</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02688756585121155</v>
+        <v>0.1704817414283752</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06410676240921021</v>
+        <v>0.09751029312610626</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.06533961743116379</v>
+        <v>0.01447326689958572</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03731640055775642</v>
+        <v>0.08184223622083664</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.04587128013372421</v>
+        <v>0.0280090756714344</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0141366720199585</v>
+        <v>0.08766116201877594</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.02385378628969193</v>
+        <v>0.0861203521490097</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.001635940745472908</v>
+        <v>0.1232262998819351</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.006334815640002489</v>
+        <v>0.1133904531598091</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.03552890941500664</v>
+        <v>0.1474708169698715</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01248682476580143</v>
+        <v>0.0628942996263504</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03772177919745445</v>
+        <v>0.1520171463489532</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.003221596591174603</v>
+        <v>0.06892078369855881</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0209316611289978</v>
+        <v>0.1095233857631683</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.00869383942335844</v>
+        <v>0.1037991940975189</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.07135650515556335</v>
+        <v>0.003086168318986893</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.03477921709418297</v>
+        <v>0.02337411791086197</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0008224444463849068</v>
+        <v>0.05833210051059723</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.02195542305707932</v>
+        <v>0.01022065989673138</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.07883424311876297</v>
+        <v>0.02757467329502106</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1467837542295456</v>
+        <v>0.3532535135746002</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.049000583589077</v>
+        <v>0.008140020072460175</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0002380609512329102</v>
+        <v>0.1903280913829803</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06694317609071732</v>
+        <v>0.1365238726139069</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0650244727730751</v>
+        <v>0.01693204045295715</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.01929721236228943</v>
+        <v>0.03270275518298149</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.002429206855595112</v>
+        <v>0.06683168560266495</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.06612485647201538</v>
+        <v>0.1004439443349838</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.09108491241931915</v>
+        <v>0.0244160071015358</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.1030858904123306</v>
+        <v>0.01489483565092087</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.06671108305454254</v>
+        <v>0.09255640208721161</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.02985335886478424</v>
+        <v>0.01863723993301392</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1208131164312363</v>
+        <v>0.03725727647542953</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001768971211276948</v>
+        <v>0.1487255394458771</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.05642754584550858</v>
+        <v>0.06045028567314148</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1432172805070877</v>
+        <v>0.08298290520906448</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.002257874701172113</v>
+        <v>0.006710922345519066</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.04685211181640625</v>
+        <v>0.08232741802930832</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.044378362596035</v>
+        <v>0.02348822727799416</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.04714317992329597</v>
+        <v>0.09502574801445007</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.01308125350624323</v>
+        <v>0.05066365003585815</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.08646470308303833</v>
+        <v>0.01619016006588936</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.009410659782588482</v>
+        <v>0.01485961955040693</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.05516798794269562</v>
+        <v>0.06909950077533722</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.02899387292563915</v>
+        <v>0.05090457573533058</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0424654558300972</v>
+        <v>0.1440166682004929</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.06164299696683884</v>
+        <v>0.01475262269377708</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.06865137070417404</v>
+        <v>0.3423596024513245</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.007204134482890368</v>
+        <v>0.02658351138234138</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0426785908639431</v>
+        <v>0.2444040179252625</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05223142355680466</v>
+        <v>0.05599289387464523</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.02421516925096512</v>
+        <v>0.0471009686589241</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.02880189754068851</v>
+        <v>0.08133141696453094</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0335746556520462</v>
+        <v>0.02139156684279442</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.060544453561306</v>
+        <v>0.1570560038089752</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0274403840303421</v>
+        <v>0.006377669982612133</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.05701301246881485</v>
+        <v>0.2213368564844131</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.01822507008910179</v>
+        <v>0.04187868908047676</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.006820843555033207</v>
+        <v>0.1000225991010666</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05448154360055923</v>
+        <v>0.03966175764799118</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.02360467985272408</v>
+        <v>0.08717945218086243</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0001336508430540562</v>
+        <v>0.003040476702153683</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.01060642395168543</v>
+        <v>0.0399240180850029</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.03253401443362236</v>
+        <v>0.03706847131252289</v>
       </c>
       <c r="CM15" t="n">
-        <v>3.889389336109161e-05</v>
+        <v>0.02363394200801849</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.004253196530044079</v>
+        <v>0.1757128536701202</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.02268070168793201</v>
+        <v>0.04595275968313217</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.004058755002915859</v>
+        <v>0.1129511743783951</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.05562947317957878</v>
+        <v>0.2272125631570816</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0677511915564537</v>
+        <v>0.1782242655754089</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.04911007732152939</v>
+        <v>0.2171471267938614</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0389421246945858</v>
+        <v>0.2294886857271194</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.02973541244864464</v>
+        <v>0.05916053056716919</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.02139902673661709</v>
+        <v>0.002234701998531818</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.06112863123416901</v>
+        <v>0.2153057307004929</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.006969481706619263</v>
+        <v>0.02903443016111851</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.01568698324263096</v>
+        <v>0.123759001493454</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03337304666638374</v>
+        <v>0.072895847260952</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01448743045330048</v>
+        <v>0.08991581946611404</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.007296061143279076</v>
+        <v>0.0275159664452076</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.001995624275878072</v>
+        <v>0.02877291850745678</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.03493507578969002</v>
+        <v>0.07059809565544128</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.01226180978119373</v>
+        <v>0.0245082788169384</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1862061768770218</v>
+        <v>0.02113145589828491</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.01821448467671871</v>
+        <v>0.0437963679432869</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.1014569625258446</v>
+        <v>0.1455927640199661</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01962137222290039</v>
+        <v>0.1037080138921738</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.07696038484573364</v>
+        <v>0.4336690604686737</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.1000258699059486</v>
+        <v>0.1225062981247902</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01129746157675982</v>
+        <v>0.0002238526940345764</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.03954071551561356</v>
+        <v>0.04057800024747849</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.04867422580718994</v>
+        <v>0.01477312669157982</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03695874288678169</v>
+        <v>0.1804615408182144</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1318580061197281</v>
+        <v>0.1013420820236206</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.03582952171564102</v>
+        <v>0.08027756214141846</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.09255951642990112</v>
+        <v>0.02172054350376129</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06663484871387482</v>
+        <v>0.004190359264612198</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.002104154322296381</v>
+        <v>0.01541489362716675</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.03277913108468056</v>
+        <v>0.03463505581021309</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.009382856078445911</v>
+        <v>0.2112690955400467</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.01477952115237713</v>
+        <v>0.00556087214499712</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01286192797124386</v>
+        <v>0.1526102870702744</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.04520725458860397</v>
+        <v>0.01959325186908245</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.04961615055799484</v>
+        <v>0.02891271747648716</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.008361461572349072</v>
+        <v>0.08096159994602203</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.06139134243130684</v>
+        <v>0.2884534001350403</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01948575861752033</v>
+        <v>0.09425203502178192</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.02733869478106499</v>
+        <v>0.1537804901599884</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.001627064310014248</v>
+        <v>0.1202021017670631</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.03540321439504623</v>
+        <v>0.02497635222971439</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.04732086509466171</v>
+        <v>0.2729309499263763</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.001394644612446427</v>
+        <v>0.06637317687273026</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.015758216381073</v>
+        <v>0.0608341209590435</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.02095152623951435</v>
+        <v>0.01076921634376049</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.02796664461493492</v>
+        <v>0.0796448290348053</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.007290026172995567</v>
+        <v>0.02576413936913013</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.02443895116448402</v>
+        <v>0.02807396277785301</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.03948304429650307</v>
+        <v>0.02998787350952625</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.01539623085409403</v>
+        <v>0.1442863792181015</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04988768696784973</v>
+        <v>0.2580226361751556</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.003555390285328031</v>
+        <v>0.04392824321985245</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.01176085788756609</v>
+        <v>0.2243159413337708</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01291779614984989</v>
+        <v>0.0932878777384758</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0117482328787446</v>
+        <v>0.06139598041772842</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.04856350272893906</v>
+        <v>0.1066710129380226</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.03426959738135338</v>
+        <v>0.128337487578392</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.01026364229619503</v>
+        <v>0.007012802641838789</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.020384406670928</v>
+        <v>0.01532038487493992</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.07181982696056366</v>
+        <v>0.2760097682476044</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.02359138801693916</v>
+        <v>0.03314381465315819</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.008843928575515747</v>
+        <v>0.111418105661869</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03318938612937927</v>
+        <v>0.05864075571298599</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01694805733859539</v>
+        <v>0.1045788750052452</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.02271432802081108</v>
+        <v>0.02477199956774712</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0005143575835973024</v>
+        <v>0.05008191615343094</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.04068920761346817</v>
+        <v>0.07381659746170044</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.01261715590953827</v>
+        <v>0.08733315765857697</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.02541374415159225</v>
+        <v>0.07541190832853317</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.03636208921670914</v>
+        <v>0.06364475190639496</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.002486696001142263</v>
+        <v>0.002169518731534481</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.04569472745060921</v>
+        <v>0.02439899742603302</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.04695810005068779</v>
+        <v>0.09897124767303467</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.01617163605988026</v>
+        <v>0.06064286082983017</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.008648483082652092</v>
+        <v>0.05300994217395782</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0251038521528244</v>
+        <v>0.1947511583566666</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.123902902007103</v>
+        <v>0.1260245591402054</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.06929440051317215</v>
+        <v>0.05218349769711494</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.1216369494795799</v>
+        <v>0.1069784462451935</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.005615214817225933</v>
+        <v>0.4567859470844269</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.04357064887881279</v>
+        <v>0.1916937083005905</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0590314194560051</v>
+        <v>0.1412071734666824</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.01130188815295696</v>
+        <v>0.1882886290550232</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.009508280083537102</v>
+        <v>0.1066217869520187</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.02645019814372063</v>
+        <v>0.02914329618215561</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02875741198658943</v>
+        <v>0.04561205953359604</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.04298746213316917</v>
+        <v>0.04796097427606583</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.01150720193982124</v>
+        <v>0.009577803313732147</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.01620853319764137</v>
+        <v>0.001373011618852615</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.1107088029384613</v>
+        <v>0.1135865151882172</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.06364257633686066</v>
+        <v>0.1174332648515701</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.05269480869174004</v>
+        <v>0.01606700755655766</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.007203650195151567</v>
+        <v>0.1629994958639145</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.005148413591086864</v>
+        <v>0.08390187472105026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.001070183236151934</v>
+        <v>3.064272732444806e-06</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0005242241895757616</v>
+        <v>6.250986916711554e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002682355465367436</v>
+        <v>0.0001050735445460305</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002169081708416343</v>
+        <v>0.0001358952140435576</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001418792875483632</v>
+        <v>2.275431688758545e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0005740289343520999</v>
+        <v>5.132637306815013e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005921581177972257</v>
+        <v>2.928323920059483e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003173980803694576</v>
+        <v>4.636339508579113e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005317417089827359</v>
+        <v>9.072011744137853e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0008868294535204768</v>
+        <v>1.967424213944469e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005035190843045712</v>
+        <v>6.69896398903802e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002056797035038471</v>
+        <v>0.0001432348362868652</v>
       </c>
       <c r="M16" t="n">
-        <v>0.002275720005854964</v>
+        <v>0.0001777704455889761</v>
       </c>
       <c r="N16" t="n">
-        <v>5.615689588012174e-05</v>
+        <v>2.935770135081839e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006294577615335584</v>
+        <v>7.641527918167412e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003370787017047405</v>
+        <v>2.52470636041835e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.25014620507136e-05</v>
+        <v>9.57212396315299e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0009769813623279333</v>
+        <v>5.232715921010822e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003254271578043699</v>
+        <v>1.750049523252528e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0004239756963215768</v>
+        <v>1.677927684795577e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004135834751650691</v>
+        <v>2.308803959749639e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0004531383456196636</v>
+        <v>2.035575380432419e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0003475963312666863</v>
+        <v>2.89886102109449e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0001731461670715362</v>
+        <v>3.722476685652509e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0003700978995766491</v>
+        <v>1.975683335331269e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0002574885438662022</v>
+        <v>1.046416582539678e-05</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.045624518766999e-05</v>
+        <v>3.300313983345404e-05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0008794124587439001</v>
+        <v>2.337867044843733e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.927968934178352e-05</v>
+        <v>9.259131729777437e-06</v>
       </c>
       <c r="AD16" t="n">
-        <v>9.643657540436834e-05</v>
+        <v>9.450022844248451e-06</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0009182635694742203</v>
+        <v>6.076493446016684e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0007593284244649112</v>
+        <v>2.146347833331674e-05</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.352655767230317e-06</v>
+        <v>2.713189132919069e-06</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.335808625910431e-05</v>
+        <v>6.055239282432012e-06</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0003171199641656131</v>
+        <v>4.169986277702264e-05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.000360210775397718</v>
+        <v>2.189804035879206e-05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0002627731009852141</v>
+        <v>7.439700311806519e-06</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.687078762799501e-05</v>
+        <v>2.805037183861714e-06</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.150512591470033e-05</v>
+        <v>2.649314774316736e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0001670619240030646</v>
+        <v>3.19922219205182e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0006517691072076559</v>
+        <v>3.410721183172427e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001562025572638959</v>
+        <v>5.502122803591192e-06</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0002959671546705067</v>
+        <v>2.582611705292948e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.092978921718895e-05</v>
+        <v>2.620771192596294e-05</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001990087330341339</v>
+        <v>3.99879427277483e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.0008846773416735232</v>
+        <v>2.270151526317932e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0009676560875959694</v>
+        <v>4.592475306708366e-07</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.001500040758401155</v>
+        <v>0.0001509800058556721</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.001869140774942935</v>
+        <v>0.000105282713775523</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0003433837846387178</v>
+        <v>8.342304681718815e-06</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.000686434970702976</v>
+        <v>7.996799831744283e-05</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0004373713163658977</v>
+        <v>7.246168388519436e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0005069856415502727</v>
+        <v>2.40375902649248e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0004045004025101662</v>
+        <v>7.154539343900979e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0007965218974277377</v>
+        <v>2.025055073318072e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.001543106860481203</v>
+        <v>1.499587415310089e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0003453704121056944</v>
+        <v>2.556304025347345e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0007806475041434169</v>
+        <v>1.718144994811155e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0006162742502056062</v>
+        <v>1.367225468129618e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.001003530924208462</v>
+        <v>2.653880073921755e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0006337865488603711</v>
+        <v>5.897433584323153e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>7.83940777182579e-07</v>
+        <v>5.789082570117898e-05</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0008492241031490266</v>
+        <v>4.756102498504333e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>4.008491669083014e-05</v>
+        <v>4.454788358998485e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0005365857505239546</v>
+        <v>3.929366357624531e-05</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.000208970857784152</v>
+        <v>1.209423498949036e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.969223689637147e-05</v>
+        <v>2.530615347495768e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0005491788615472615</v>
+        <v>3.285471393610351e-05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.463518704753369e-05</v>
+        <v>1.139606411015848e-05</v>
       </c>
       <c r="BR16" t="n">
-        <v>2.272996061947197e-05</v>
+        <v>1.499720110587077e-05</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0002855139318853617</v>
+        <v>6.739336822647601e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0002031073527177796</v>
+        <v>1.271114615519764e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.000238328633713536</v>
+        <v>1.546909516036976e-06</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0005807155393995345</v>
+        <v>2.78476181847509e-05</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.00103259552270174</v>
+        <v>8.317852189065889e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.001248363638296723</v>
+        <v>9.980591130442917e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0004832896811421961</v>
+        <v>8.210013220377732e-06</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0002305278612766415</v>
+        <v>3.034313340322115e-05</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0001171511685242876</v>
+        <v>1.948445424204692e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.000376773503376171</v>
+        <v>2.34263607126195e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0004659165279008448</v>
+        <v>4.057673504576087e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.0003178826882503927</v>
+        <v>1.178261072709574e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>6.014472091919743e-05</v>
+        <v>1.465675632061902e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.0007004234939813614</v>
+        <v>3.709683733177371e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0003655343316495419</v>
+        <v>5.303511716192588e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0003351240884512663</v>
+        <v>1.537719799671322e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>4.984392944606952e-05</v>
+        <v>1.775076270860154e-05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0002352340234210715</v>
+        <v>2.777172994683497e-06</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0001768205547705293</v>
+        <v>6.006327566865366e-06</v>
       </c>
       <c r="CL16" t="n">
-        <v>6.132340058684349e-05</v>
+        <v>1.024621633405332e-05</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0009825477609410882</v>
+        <v>1.759863152983598e-06</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0008236478315666318</v>
+        <v>1.608836646482814e-05</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.780633465386927e-05</v>
+        <v>6.082762774894945e-05</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0003929930098820478</v>
+        <v>9.478766878601164e-05</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0002285032824147493</v>
+        <v>2.571220102254301e-05</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.000305788271361962</v>
+        <v>5.695691652363166e-05</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.000214299390790984</v>
+        <v>4.617720151145477e-06</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.001059880945831537</v>
+        <v>8.08096410764847e-06</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0002232005790574476</v>
+        <v>3.542286503943615e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0002394314069533721</v>
+        <v>5.346458237909246e-06</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.000229482728173025</v>
+        <v>2.689532084332313e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0004642331041395664</v>
+        <v>3.178373663104139e-05</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.000405839120503515</v>
+        <v>4.66819983557798e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0001458048791391775</v>
+        <v>1.506243552285014e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.162644886993803e-05</v>
+        <v>2.897980994021054e-05</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0002105302119161934</v>
+        <v>3.820943675236776e-06</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0001142617402365431</v>
+        <v>7.83535506343469e-06</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.551390232634731e-05</v>
+        <v>1.222420814883662e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>8.069344039540738e-05</v>
+        <v>4.098566932952963e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0009107223595492542</v>
+        <v>3.93508598790504e-05</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.000819950713776052</v>
+        <v>1.619207523617661e-06</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0002655238495208323</v>
+        <v>2.522789691283833e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0001158177401521243</v>
+        <v>1.617865927983075e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0002451590844430029</v>
+        <v>6.380485501722433e-06</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0008671774412505329</v>
+        <v>4.280119901522994e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0002516661770641804</v>
+        <v>5.548241097130813e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.000287227361695841</v>
+        <v>5.941576091572642e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.635354758240283e-05</v>
+        <v>2.886183438022272e-06</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0006005583563819528</v>
+        <v>1.645419433771167e-05</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0004657107638195157</v>
+        <v>1.603796226845589e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>7.76882516220212e-05</v>
+        <v>1.320916908298386e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0009208928095176816</v>
+        <v>4.026188980787992e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.000384739541914314</v>
+        <v>1.184330358228181e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.0003924164338968694</v>
+        <v>2.299741026945412e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0001353481638943776</v>
+        <v>2.073518407996744e-05</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0006486767088063061</v>
+        <v>3.693005055538379e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0001973928592633456</v>
+        <v>5.071273335488513e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0008868408622220159</v>
+        <v>3.026269769179635e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0002827206335496157</v>
+        <v>2.355071774218231e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.00017662147001829</v>
+        <v>7.546991128037916e-06</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0004324231122154742</v>
+        <v>2.597574166429695e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.000594095850829035</v>
+        <v>2.583576497272588e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.5028402635362e-05</v>
+        <v>1.300418989558239e-05</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0001719928113743663</v>
+        <v>4.361866740509868e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>3.601855132728815e-05</v>
+        <v>2.003025110752787e-05</v>
       </c>
       <c r="EF16" t="n">
-        <v>2.699517244764138e-05</v>
+        <v>2.588302595540881e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0003040713490918279</v>
+        <v>2.05183205252979e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0007177659426815808</v>
+        <v>1.219030400534393e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.0008410761947743595</v>
+        <v>6.341701373457909e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>1.045762383000692e-05</v>
+        <v>1.4337202628667e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>6.241200026124716e-06</v>
+        <v>2.997167030116543e-06</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.000284853857010603</v>
+        <v>1.057297140505398e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>8.849102596286684e-05</v>
+        <v>9.050801281773602e-07</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0002963391889352351</v>
+        <v>4.278235792298801e-06</v>
       </c>
       <c r="EO16" t="n">
-        <v>2.541033609304577e-05</v>
+        <v>4.3983773139189e-06</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0005958336405456066</v>
+        <v>2.416154893580824e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0003070450620725751</v>
+        <v>1.214638450619532e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0004067666013725102</v>
+        <v>3.63583312719129e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0002109721972374246</v>
+        <v>1.427303141099401e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>9.774179488886148e-05</v>
+        <v>5.824453546665609e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0003155407612212002</v>
+        <v>4.272375917935278e-06</v>
       </c>
       <c r="EV16" t="n">
-        <v>1.3315071555553e-05</v>
+        <v>3.776823723455891e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0003410975623410195</v>
+        <v>7.261677637870889e-06</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.000243998336372897</v>
+        <v>5.432148100226186e-07</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0002914717770181596</v>
+        <v>2.055114600807428e-05</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0006130626425147057</v>
+        <v>3.642231240519322e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0003907536738552153</v>
+        <v>6.351586489472538e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0001977596548385918</v>
+        <v>1.405094008077867e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>8.900729881133884e-06</v>
+        <v>2.357304765610024e-05</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001807493099477142</v>
+        <v>5.186601811146829e-06</v>
       </c>
       <c r="FE16" t="n">
-        <v>9.517658327240497e-05</v>
+        <v>2.17209762922721e-05</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0001608886668691412</v>
+        <v>1.45528138091322e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>9.298199438489974e-05</v>
+        <v>1.398306812916417e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0004095019539818168</v>
+        <v>2.208485602750443e-05</v>
       </c>
       <c r="FI16" t="n">
-        <v>1.380120556859765e-05</v>
+        <v>8.013086699065752e-06</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0004054601886309683</v>
+        <v>2.634986776683945e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0002826677518896759</v>
+        <v>8.841501767165028e-06</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0003187778347637504</v>
+        <v>3.385278978385031e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0001936134358402342</v>
+        <v>8.276451808342244e-06</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0004320171719882637</v>
+        <v>1.102314490708522e-05</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0002905826841015369</v>
+        <v>5.018142474000342e-06</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0004354143457021564</v>
+        <v>8.164264727383852e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0002307973627466708</v>
+        <v>1.836224691942334e-05</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0006244128453545272</v>
+        <v>2.812497041304596e-05</v>
       </c>
       <c r="FS16" t="n">
-        <v>5.568485357798636e-05</v>
+        <v>1.278006038774038e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>4.509325663093477e-05</v>
+        <v>7.352170359808952e-05</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0003437700506765395</v>
+        <v>2.865882379410323e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001237188844243065</v>
+        <v>2.626672358019277e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.000308311078697443</v>
+        <v>3.693263352033682e-05</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.000107096871943213</v>
+        <v>1.858088035078254e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.000135502777993679</v>
+        <v>3.106497752014548e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0005420373636297882</v>
+        <v>2.308529656147584e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>9.501620661467314e-05</v>
+        <v>1.095524567062967e-05</v>
       </c>
       <c r="GB16" t="n">
-        <v>4.416062438394874e-06</v>
+        <v>6.206709804246202e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0005632381653413177</v>
+        <v>1.388840155414073e-05</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0008309768163599074</v>
+        <v>3.829242268693633e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0002630728995427489</v>
+        <v>8.581333531765267e-06</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0001499563513789326</v>
+        <v>2.458778544678353e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>2.216751818195917e-05</v>
+        <v>4.33377645094879e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.99786017119186e-06</v>
+        <v>2.820008376147598e-06</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0001210503105539829</v>
+        <v>1.501924452895764e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>1.985249036806636e-05</v>
+        <v>2.000200311158551e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>4.851119956583716e-05</v>
+        <v>5.65989194001304e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>5.99705490458291e-05</v>
+        <v>6.623610261158319e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>5.99590057390742e-05</v>
+        <v>1.551083187223412e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>2.350299109821208e-05</v>
+        <v>3.45855914929416e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>2.821531234076247e-05</v>
+        <v>1.946955853782129e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>9.561234037391841e-06</v>
+        <v>2.114098833772005e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>1.15713646664517e-05</v>
+        <v>6.891664270369802e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>9.425223834114149e-05</v>
+        <v>2.192974898207467e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>3.524062094584224e-06</v>
+        <v>1.878345074146637e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>3.06061738228891e-05</v>
+        <v>1.162763328466099e-05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.385720967547968e-05</v>
+        <v>1.095031439035665e-05</v>
       </c>
       <c r="O17" t="n">
-        <v>5.345715180737898e-05</v>
+        <v>1.451306707167532e-05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.537144064262975e-05</v>
+        <v>6.08816162639414e-06</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.556904968922026e-06</v>
+        <v>1.116858402383514e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>8.909118150768336e-06</v>
+        <v>2.164533270843094e-06</v>
       </c>
       <c r="S17" t="n">
-        <v>8.957767363426683e-07</v>
+        <v>3.049495262530399e-06</v>
       </c>
       <c r="T17" t="n">
-        <v>1.708003583189566e-05</v>
+        <v>3.223383600925445e-06</v>
       </c>
       <c r="U17" t="n">
-        <v>2.826865511451615e-06</v>
+        <v>1.374986254631949e-06</v>
       </c>
       <c r="V17" t="n">
-        <v>2.217849578300957e-05</v>
+        <v>1.095440666176728e-06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.722491288091987e-05</v>
+        <v>8.390696848437074e-08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.863746183516923e-05</v>
+        <v>1.956051391971414e-06</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.268486231419956e-06</v>
+        <v>4.076488949067425e-06</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.6638012311887e-05</v>
+        <v>6.140078312455444e-07</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.982203664549161e-06</v>
+        <v>3.163972905895207e-06</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.672882929909974e-06</v>
+        <v>6.660404324065894e-06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.362447073915973e-05</v>
+        <v>3.639767328422749e-06</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1707692212658e-06</v>
+        <v>2.952680461021373e-06</v>
       </c>
       <c r="AE17" t="n">
-        <v>8.614036232756916e-06</v>
+        <v>2.760856432360015e-06</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.512737071607262e-06</v>
+        <v>8.960117156675551e-06</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.681379778048722e-06</v>
+        <v>2.963019824164803e-06</v>
       </c>
       <c r="AH17" t="n">
-        <v>9.081031748792157e-06</v>
+        <v>3.990094228356611e-07</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.091428753687069e-06</v>
+        <v>4.92102208227152e-06</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.920727860735497e-06</v>
+        <v>2.534400891818223e-06</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.245277962880209e-05</v>
+        <v>2.169974095522775e-06</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.221997783635743e-05</v>
+        <v>9.726550160849001e-07</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.563771886343602e-06</v>
+        <v>4.718174295703648e-07</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.894257578300312e-06</v>
+        <v>1.018639181893377e-06</v>
       </c>
       <c r="AO17" t="n">
-        <v>3.859800017380621e-06</v>
+        <v>7.117372661014087e-06</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.335721364943311e-05</v>
+        <v>4.387471562949941e-06</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.003376837616088e-06</v>
+        <v>4.240107955411077e-06</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.099936980608618e-05</v>
+        <v>5.299601525621256e-06</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.406978662998881e-05</v>
+        <v>4.133318725507706e-06</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.337956049013883e-06</v>
+        <v>1.370254949506489e-06</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.235047425841913e-05</v>
+        <v>2.512751598260365e-05</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.251908088306664e-05</v>
+        <v>7.030394044704735e-08</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.714693204732612e-06</v>
+        <v>2.686279913177714e-06</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.00087160919793e-05</v>
+        <v>1.051206982083386e-05</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.587641549529508e-05</v>
+        <v>1.492365845479071e-05</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.736048716338701e-06</v>
+        <v>1.622139734536177e-06</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.80827992153354e-05</v>
+        <v>3.444735739321914e-06</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.518105798633769e-06</v>
+        <v>7.449785698554479e-06</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.679400485154474e-06</v>
+        <v>1.171397912003158e-06</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.942867675097659e-05</v>
+        <v>1.8020318748313e-06</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.146295082638972e-05</v>
+        <v>7.496131502193748e-07</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.443008113710675e-05</v>
+        <v>2.085956793962396e-06</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.419406468514353e-05</v>
+        <v>2.936648115792195e-06</v>
       </c>
       <c r="BH17" t="n">
-        <v>1.164966852229554e-05</v>
+        <v>7.481095849470876e-07</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.768121910572518e-05</v>
+        <v>2.752242153292173e-06</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.925318065332249e-05</v>
+        <v>1.158948634838453e-05</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.859113454993349e-06</v>
+        <v>1.615713244973449e-06</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.097332824429031e-05</v>
+        <v>1.234632577507e-06</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.879385465348605e-05</v>
+        <v>8.56266706250608e-06</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.285343296331121e-05</v>
+        <v>2.599764684418915e-06</v>
       </c>
       <c r="BO17" t="n">
-        <v>7.834205462131649e-06</v>
+        <v>5.454072834254475e-06</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.273137170050177e-06</v>
+        <v>9.764075912244152e-06</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.656017598696053e-06</v>
+        <v>3.596743681555381e-06</v>
       </c>
       <c r="BR17" t="n">
-        <v>4.705586434283759e-06</v>
+        <v>1.83980318979593e-06</v>
       </c>
       <c r="BS17" t="n">
-        <v>5.951725142949726e-06</v>
+        <v>2.654201125551481e-07</v>
       </c>
       <c r="BT17" t="n">
-        <v>9.168913493340369e-06</v>
+        <v>2.678479859241634e-06</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.703675353492144e-06</v>
+        <v>4.881116183241829e-06</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.076784873381257e-05</v>
+        <v>1.098684333555866e-05</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.474816392350476e-05</v>
+        <v>7.020809107416426e-07</v>
       </c>
       <c r="BX17" t="n">
-        <v>1.113477264880203e-05</v>
+        <v>1.646340024308302e-06</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.577339753566775e-05</v>
+        <v>1.465861032556859e-06</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.891796379524749e-06</v>
+        <v>3.10607310893829e-06</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.764526915503666e-06</v>
+        <v>5.445352144306526e-06</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.685876203642692e-06</v>
+        <v>3.101925813098205e-06</v>
       </c>
       <c r="CC17" t="n">
-        <v>1.051495837600669e-05</v>
+        <v>3.420341045057285e-06</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.33011643710779e-08</v>
+        <v>7.07156118551211e-07</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.869632615125738e-05</v>
+        <v>3.900501269527012e-06</v>
       </c>
       <c r="CF17" t="n">
-        <v>7.360177733062301e-06</v>
+        <v>6.291472232078377e-08</v>
       </c>
       <c r="CG17" t="n">
-        <v>8.03492366685532e-06</v>
+        <v>4.505932906795351e-07</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.908392164295947e-07</v>
+        <v>5.045823854743503e-06</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.136659011535812e-05</v>
+        <v>2.753663920884719e-06</v>
       </c>
       <c r="CJ17" t="n">
-        <v>4.879997050011298e-06</v>
+        <v>9.974911563404021e-07</v>
       </c>
       <c r="CK17" t="n">
-        <v>4.150319000473246e-06</v>
+        <v>1.102603619074216e-06</v>
       </c>
       <c r="CL17" t="n">
-        <v>5.830835107190069e-06</v>
+        <v>2.211531295870373e-07</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.902221265481785e-05</v>
+        <v>3.388777713553282e-06</v>
       </c>
       <c r="CN17" t="n">
-        <v>7.190580618043896e-06</v>
+        <v>1.226491804118268e-05</v>
       </c>
       <c r="CO17" t="n">
-        <v>5.703848728444427e-06</v>
+        <v>3.491870756988646e-06</v>
       </c>
       <c r="CP17" t="n">
-        <v>6.001099791319575e-06</v>
+        <v>1.075182353815762e-06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>1.190149032481713e-05</v>
+        <v>8.334308404300828e-06</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.00989309430588e-05</v>
+        <v>2.072724782919977e-06</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.205769851570949e-05</v>
+        <v>1.268221240025014e-06</v>
       </c>
       <c r="CT17" t="n">
-        <v>1.772862560756039e-05</v>
+        <v>2.176391035391134e-06</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.520919568065437e-06</v>
+        <v>1.022293645291938e-06</v>
       </c>
       <c r="CV17" t="n">
-        <v>3.331754214741522e-07</v>
+        <v>3.727633384187357e-07</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.57350477820728e-05</v>
+        <v>4.267047643224942e-06</v>
       </c>
       <c r="CX17" t="n">
-        <v>8.420531230513006e-06</v>
+        <v>7.348609187829425e-07</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.27651946968399e-05</v>
+        <v>1.404047907271888e-06</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.852504283306189e-06</v>
+        <v>2.70377586275572e-06</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.579371746629477e-05</v>
+        <v>3.274489245086443e-06</v>
       </c>
       <c r="DB17" t="n">
-        <v>3.112233571300749e-06</v>
+        <v>2.382241063969559e-06</v>
       </c>
       <c r="DC17" t="n">
-        <v>7.459331754944287e-06</v>
+        <v>2.511306433916616e-07</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.462197133150767e-06</v>
+        <v>3.54954920567252e-07</v>
       </c>
       <c r="DE17" t="n">
-        <v>4.726956831291318e-06</v>
+        <v>2.321797865079134e-07</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.462342126818839e-05</v>
+        <v>7.63554544391809e-06</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.535534117167117e-06</v>
+        <v>5.890164175070822e-06</v>
       </c>
       <c r="DH17" t="n">
-        <v>3.206069231964648e-05</v>
+        <v>2.196413106503314e-06</v>
       </c>
       <c r="DI17" t="n">
-        <v>7.966709745232947e-06</v>
+        <v>3.075803078900208e-06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.281285671619116e-06</v>
+        <v>7.269149136845954e-06</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.93261839740444e-05</v>
+        <v>2.551528041294659e-06</v>
       </c>
       <c r="DL17" t="n">
-        <v>1.305141449847724e-05</v>
+        <v>3.896832822647411e-06</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.177073045255383e-05</v>
+        <v>6.838100489403587e-06</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.026999133406207e-06</v>
+        <v>4.047645916216425e-07</v>
       </c>
       <c r="DO17" t="n">
-        <v>7.914016350696329e-06</v>
+        <v>2.547336862335214e-06</v>
       </c>
       <c r="DP17" t="n">
-        <v>1.647102408242063e-06</v>
+        <v>2.035333750427526e-07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>3.618323944465374e-06</v>
+        <v>8.276578228105791e-06</v>
       </c>
       <c r="DR17" t="n">
-        <v>2.525655872887e-06</v>
+        <v>1.091463445845875e-06</v>
       </c>
       <c r="DS17" t="n">
-        <v>1.193718890135642e-05</v>
+        <v>3.640914655989036e-06</v>
       </c>
       <c r="DT17" t="n">
-        <v>5.891160526516614e-06</v>
+        <v>1.100257577490993e-06</v>
       </c>
       <c r="DU17" t="n">
-        <v>7.634464054717682e-06</v>
+        <v>9.894781669572694e-07</v>
       </c>
       <c r="DV17" t="n">
-        <v>6.310720436886186e-06</v>
+        <v>4.945366526953876e-06</v>
       </c>
       <c r="DW17" t="n">
-        <v>3.048755843337858e-06</v>
+        <v>2.77803155768197e-06</v>
       </c>
       <c r="DX17" t="n">
-        <v>2.338362946829875e-06</v>
+        <v>2.613888455016422e-06</v>
       </c>
       <c r="DY17" t="n">
-        <v>1.289136616833275e-05</v>
+        <v>2.152309434677591e-06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.322751586485538e-06</v>
+        <v>2.9435118449328e-06</v>
       </c>
       <c r="EA17" t="n">
-        <v>5.04848458149354e-06</v>
+        <v>9.960127499653026e-06</v>
       </c>
       <c r="EB17" t="n">
-        <v>4.525616532191634e-06</v>
+        <v>3.137220573989907e-06</v>
       </c>
       <c r="EC17" t="n">
-        <v>8.512369049640256e-07</v>
+        <v>6.319833687484788e-07</v>
       </c>
       <c r="ED17" t="n">
-        <v>8.572059414291289e-06</v>
+        <v>7.277817076101201e-06</v>
       </c>
       <c r="EE17" t="n">
-        <v>6.937707439647056e-07</v>
+        <v>4.850830464420142e-06</v>
       </c>
       <c r="EF17" t="n">
-        <v>5.773405973741319e-06</v>
+        <v>3.361204790053307e-07</v>
       </c>
       <c r="EG17" t="n">
-        <v>1.540171251690481e-05</v>
+        <v>4.297627640426072e-07</v>
       </c>
       <c r="EH17" t="n">
-        <v>9.544208296574652e-06</v>
+        <v>6.3246682202589e-07</v>
       </c>
       <c r="EI17" t="n">
-        <v>2.803829374897759e-06</v>
+        <v>1.059133774106158e-05</v>
       </c>
       <c r="EJ17" t="n">
-        <v>8.28500105853891e-06</v>
+        <v>4.775668571710412e-07</v>
       </c>
       <c r="EK17" t="n">
-        <v>8.511537089361809e-06</v>
+        <v>2.915665390901268e-06</v>
       </c>
       <c r="EL17" t="n">
-        <v>5.96288464294048e-06</v>
+        <v>4.492935659072828e-07</v>
       </c>
       <c r="EM17" t="n">
-        <v>2.707903831833391e-06</v>
+        <v>1.734794977892307e-06</v>
       </c>
       <c r="EN17" t="n">
-        <v>6.714560640830314e-08</v>
+        <v>3.041206468878954e-07</v>
       </c>
       <c r="EO17" t="n">
-        <v>5.163519745110534e-06</v>
+        <v>1.551955620016088e-06</v>
       </c>
       <c r="EP17" t="n">
-        <v>8.14022496342659e-06</v>
+        <v>1.045700514623604e-06</v>
       </c>
       <c r="EQ17" t="n">
-        <v>1.370988411508733e-05</v>
+        <v>1.149768650066108e-06</v>
       </c>
       <c r="ER17" t="n">
-        <v>1.606374280527234e-05</v>
+        <v>3.791531298702466e-06</v>
       </c>
       <c r="ES17" t="n">
-        <v>9.645586942497175e-06</v>
+        <v>4.326055204728618e-06</v>
       </c>
       <c r="ET17" t="n">
-        <v>1.535720366518945e-05</v>
+        <v>5.257423708826536e-06</v>
       </c>
       <c r="EU17" t="n">
-        <v>6.501652933366131e-06</v>
+        <v>3.670025080282358e-06</v>
       </c>
       <c r="EV17" t="n">
-        <v>1.951166268554516e-05</v>
+        <v>1.120768502005376e-06</v>
       </c>
       <c r="EW17" t="n">
-        <v>2.271710400236771e-06</v>
+        <v>1.556538791191997e-06</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.790878741303459e-06</v>
+        <v>3.70524844583997e-07</v>
       </c>
       <c r="EY17" t="n">
-        <v>1.46308357216185e-05</v>
+        <v>4.847322088608053e-06</v>
       </c>
       <c r="EZ17" t="n">
-        <v>5.551692993321922e-06</v>
+        <v>3.261174867930094e-07</v>
       </c>
       <c r="FA17" t="n">
-        <v>1.215464271808742e-05</v>
+        <v>4.821288257517153e-07</v>
       </c>
       <c r="FB17" t="n">
-        <v>2.924494765466079e-06</v>
+        <v>3.833007212961093e-06</v>
       </c>
       <c r="FC17" t="n">
-        <v>1.222731953021139e-05</v>
+        <v>2.694489467103267e-06</v>
       </c>
       <c r="FD17" t="n">
-        <v>7.215533969429089e-06</v>
+        <v>6.720023293382837e-07</v>
       </c>
       <c r="FE17" t="n">
-        <v>6.210501851455774e-06</v>
+        <v>1.988077826808876e-07</v>
       </c>
       <c r="FF17" t="n">
-        <v>6.7107830545865e-06</v>
+        <v>9.005345305013179e-07</v>
       </c>
       <c r="FG17" t="n">
-        <v>6.739264790667221e-06</v>
+        <v>1.03980028143269e-06</v>
       </c>
       <c r="FH17" t="n">
-        <v>1.061777220456861e-05</v>
+        <v>2.31889248425432e-06</v>
       </c>
       <c r="FI17" t="n">
-        <v>8.46879538585199e-06</v>
+        <v>5.253381232250831e-07</v>
       </c>
       <c r="FJ17" t="n">
-        <v>1.66459667525487e-05</v>
+        <v>4.731484295916744e-06</v>
       </c>
       <c r="FK17" t="n">
-        <v>4.931749117531581e-06</v>
+        <v>4.40629310105578e-06</v>
       </c>
       <c r="FL17" t="n">
-        <v>9.084741577680688e-06</v>
+        <v>5.912025926591014e-07</v>
       </c>
       <c r="FM17" t="n">
-        <v>3.594415375118842e-06</v>
+        <v>2.14779720408842e-06</v>
       </c>
       <c r="FN17" t="n">
-        <v>8.135753887472674e-06</v>
+        <v>6.353175194817595e-07</v>
       </c>
       <c r="FO17" t="n">
-        <v>8.220767085731495e-06</v>
+        <v>8.28431893751258e-06</v>
       </c>
       <c r="FP17" t="n">
-        <v>2.534372470108792e-06</v>
+        <v>1.903517841128632e-07</v>
       </c>
       <c r="FQ17" t="n">
-        <v>4.386961336422246e-06</v>
+        <v>1.559872544021346e-06</v>
       </c>
       <c r="FR17" t="n">
-        <v>1.104487273551058e-05</v>
+        <v>2.927699824795127e-07</v>
       </c>
       <c r="FS17" t="n">
-        <v>1.957268614205532e-05</v>
+        <v>7.282102160388604e-06</v>
       </c>
       <c r="FT17" t="n">
-        <v>9.523603694105987e-06</v>
+        <v>9.90222815744346e-06</v>
       </c>
       <c r="FU17" t="n">
-        <v>1.945634039657307e-06</v>
+        <v>5.812241397507023e-06</v>
       </c>
       <c r="FV17" t="n">
-        <v>8.538063411833718e-06</v>
+        <v>9.544737622491084e-06</v>
       </c>
       <c r="FW17" t="n">
-        <v>6.747131919837557e-06</v>
+        <v>1.290506952500436e-05</v>
       </c>
       <c r="FX17" t="n">
-        <v>8.983845418697456e-07</v>
+        <v>3.934900632884819e-06</v>
       </c>
       <c r="FY17" t="n">
-        <v>2.253436468890868e-05</v>
+        <v>3.43157580573461e-06</v>
       </c>
       <c r="FZ17" t="n">
-        <v>8.484075806336477e-07</v>
+        <v>2.448884515615646e-06</v>
       </c>
       <c r="GA17" t="n">
-        <v>4.361500941740815e-06</v>
+        <v>2.975149300254998e-06</v>
       </c>
       <c r="GB17" t="n">
-        <v>1.153936864284333e-05</v>
+        <v>1.714841118882759e-06</v>
       </c>
       <c r="GC17" t="n">
-        <v>1.167244045063853e-05</v>
+        <v>1.792594730432029e-07</v>
       </c>
       <c r="GD17" t="n">
-        <v>1.639102265471593e-05</v>
+        <v>2.458803919580532e-06</v>
       </c>
       <c r="GE17" t="n">
-        <v>4.67333520646207e-05</v>
+        <v>4.75497745355824e-06</v>
       </c>
       <c r="GF17" t="n">
-        <v>5.13345639774343e-07</v>
+        <v>3.715263574122218e-06</v>
       </c>
       <c r="GG17" t="n">
-        <v>1.356988605039078e-06</v>
+        <v>2.708704016640695e-07</v>
       </c>
     </row>
   </sheetData>
